--- a/RESULTADOS T6.xlsx
+++ b/RESULTADOS T6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B24170-CAC4-4955-BAF4-7D419903055D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235F652D-1B29-4AFF-BD3C-C52C5EBBAEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -227,7 +227,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -330,13 +330,58 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -401,6 +446,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -731,47 +803,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A1" s="7">
+      <c r="A1" s="5">
         <v>46034</v>
       </c>
-      <c r="B1" s="8">
+      <c r="B1" s="6">
         <v>0.58333333333333337</v>
       </c>
-      <c r="C1" s="13">
+      <c r="C1" s="15">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="3">
-        <v>11</v>
-      </c>
-      <c r="G1" s="3">
+      <c r="F1" s="1">
+        <v>11</v>
+      </c>
+      <c r="G1" s="1">
         <v>8</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="1">
         <v>4</v>
       </c>
-      <c r="I1" s="3">
-        <v>11</v>
-      </c>
-      <c r="J1" s="3">
+      <c r="I1" s="1">
+        <v>11</v>
+      </c>
+      <c r="J1" s="1">
         <v>10</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="1">
         <v>12</v>
       </c>
-      <c r="L1" s="3">
+      <c r="L1" s="1">
         <v>5</v>
       </c>
-      <c r="M1" s="3">
-        <v>11</v>
-      </c>
-      <c r="N1" s="3"/>
-      <c r="O1" s="3"/>
+      <c r="M1" s="1">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1"/>
+      <c r="O1" s="24"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
@@ -814,7 +886,7 @@
         <v>11</v>
       </c>
       <c r="N2" s="4"/>
-      <c r="O2" s="4"/>
+      <c r="O2" s="26"/>
     </row>
     <row r="3" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
@@ -849,7 +921,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="3"/>
+      <c r="O3" s="25"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
@@ -892,7 +964,7 @@
         <v>10</v>
       </c>
       <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
+      <c r="O4" s="24"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -931,7 +1003,7 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="3"/>
+      <c r="O5" s="25"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
@@ -966,7 +1038,7 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="3"/>
+      <c r="O6" s="25"/>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
@@ -1001,7 +1073,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
+      <c r="O7" s="27"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
@@ -1040,7 +1112,7 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
+      <c r="O8" s="24"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
@@ -1085,7 +1157,7 @@
       <c r="N9" s="3">
         <v>3</v>
       </c>
-      <c r="O9" s="3">
+      <c r="O9" s="25">
         <v>11</v>
       </c>
     </row>
@@ -1126,7 +1198,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
+      <c r="O10" s="26"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
@@ -1161,7 +1233,7 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="3"/>
+      <c r="O11" s="25"/>
     </row>
     <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
@@ -1200,7 +1272,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" s="27"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
@@ -1245,7 +1317,7 @@
       <c r="N13" s="1">
         <v>15</v>
       </c>
-      <c r="O13" s="1">
+      <c r="O13" s="24">
         <v>13</v>
       </c>
     </row>
@@ -1290,7 +1362,7 @@
         <v>11</v>
       </c>
       <c r="N14" s="3"/>
-      <c r="O14" s="3"/>
+      <c r="O14" s="25"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
@@ -1329,7 +1401,7 @@
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
-      <c r="O15" s="4"/>
+      <c r="O15" s="26"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
@@ -1364,7 +1436,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
+      <c r="O16" s="25"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
@@ -1399,7 +1471,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+      <c r="O17" s="27"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
@@ -1438,7 +1510,7 @@
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
+      <c r="O18" s="24"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
@@ -1477,7 +1549,7 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-      <c r="O19" s="3"/>
+      <c r="O19" s="25"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
@@ -1516,7 +1588,7 @@
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
-      <c r="O20" s="4"/>
+      <c r="O20" s="26"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
@@ -1551,7 +1623,7 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
-      <c r="O21" s="3"/>
+      <c r="O21" s="25"/>
     </row>
     <row r="22" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
@@ -1596,7 +1668,7 @@
       <c r="N22" s="2">
         <v>11</v>
       </c>
-      <c r="O22" s="2">
+      <c r="O22" s="27">
         <v>7</v>
       </c>
     </row>
@@ -1637,7 +1709,7 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
+      <c r="O23" s="24"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
@@ -1676,7 +1748,7 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
-      <c r="O24" s="3"/>
+      <c r="O24" s="25"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
@@ -1711,7 +1783,7 @@
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
-      <c r="O25" s="4"/>
+      <c r="O25" s="26"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
@@ -1750,7 +1822,7 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
-      <c r="O26" s="3"/>
+      <c r="O26" s="25"/>
     </row>
     <row r="27" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
@@ -1793,7 +1865,7 @@
         <v>11</v>
       </c>
       <c r="N27" s="16"/>
-      <c r="O27" s="16"/>
+      <c r="O27" s="28"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
@@ -1838,7 +1910,7 @@
       <c r="N28" s="1">
         <v>11</v>
       </c>
-      <c r="O28" s="1">
+      <c r="O28" s="24">
         <v>7</v>
       </c>
     </row>
@@ -1885,7 +1957,7 @@
       <c r="N29" s="4">
         <v>2</v>
       </c>
-      <c r="O29" s="4">
+      <c r="O29" s="26">
         <v>11</v>
       </c>
     </row>
@@ -1926,7 +1998,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" s="27"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
@@ -1961,7 +2033,7 @@
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
+      <c r="O31" s="24"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
@@ -2004,7 +2076,7 @@
         <v>11</v>
       </c>
       <c r="N32" s="3"/>
-      <c r="O32" s="3"/>
+      <c r="O32" s="25"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
@@ -2043,7 +2115,7 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
+      <c r="O33" s="26"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
@@ -2082,7 +2154,7 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
-      <c r="O34" s="3"/>
+      <c r="O34" s="25"/>
     </row>
     <row r="35" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
@@ -2117,7 +2189,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
-      <c r="O35" s="2"/>
+      <c r="O35" s="27"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
@@ -2152,7 +2224,7 @@
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
+      <c r="O36" s="24"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
@@ -2195,7 +2267,7 @@
         <v>5</v>
       </c>
       <c r="N37" s="4"/>
-      <c r="O37" s="4"/>
+      <c r="O37" s="26"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
@@ -2238,7 +2310,7 @@
         <v>11</v>
       </c>
       <c r="N38" s="3"/>
-      <c r="O38" s="3"/>
+      <c r="O38" s="25"/>
     </row>
     <row r="39" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9">
@@ -2273,7 +2345,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
-      <c r="O39" s="2"/>
+      <c r="O39" s="27"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
@@ -2308,7 +2380,7 @@
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
+      <c r="O40" s="24"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
@@ -2353,7 +2425,7 @@
       <c r="N41" s="4">
         <v>6</v>
       </c>
-      <c r="O41" s="4">
+      <c r="O41" s="26">
         <v>11</v>
       </c>
     </row>
@@ -2398,7 +2470,7 @@
         <v>9</v>
       </c>
       <c r="N42" s="3"/>
-      <c r="O42" s="3"/>
+      <c r="O42" s="25"/>
     </row>
     <row r="43" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9">
@@ -2437,7 +2509,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
+      <c r="O43" s="27"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
@@ -2482,7 +2554,7 @@
       <c r="N44" s="1">
         <v>11</v>
       </c>
-      <c r="O44" s="1">
+      <c r="O44" s="24">
         <v>3</v>
       </c>
     </row>
@@ -2527,7 +2599,7 @@
         <v>10</v>
       </c>
       <c r="N45" s="3"/>
-      <c r="O45" s="3"/>
+      <c r="O45" s="25"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
@@ -2566,7 +2638,7 @@
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
-      <c r="O46" s="4"/>
+      <c r="O46" s="26"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
@@ -2605,7 +2677,7 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
-      <c r="O47" s="3"/>
+      <c r="O47" s="25"/>
     </row>
     <row r="48" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9">
@@ -2650,7 +2722,7 @@
       <c r="N48" s="2">
         <v>11</v>
       </c>
-      <c r="O48" s="2">
+      <c r="O48" s="27">
         <v>7</v>
       </c>
     </row>
@@ -2691,7 +2763,7 @@
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
+      <c r="O49" s="24"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
@@ -2730,7 +2802,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
-      <c r="O50" s="3"/>
+      <c r="O50" s="25"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
@@ -2769,7 +2841,7 @@
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
-      <c r="O51" s="4"/>
+      <c r="O51" s="26"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
@@ -2804,7 +2876,7 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
-      <c r="O52" s="3"/>
+      <c r="O52" s="25"/>
     </row>
     <row r="53" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9">
@@ -2849,7 +2921,7 @@
       <c r="N53" s="2">
         <v>4</v>
       </c>
-      <c r="O53" s="2">
+      <c r="O53" s="27">
         <v>11</v>
       </c>
     </row>
@@ -2894,7 +2966,7 @@
         <v>11</v>
       </c>
       <c r="N54" s="3"/>
-      <c r="O54" s="3"/>
+      <c r="O54" s="25"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
@@ -2929,7 +3001,7 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
-      <c r="O55" s="4"/>
+      <c r="O55" s="26"/>
     </row>
     <row r="56" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9">
@@ -2974,7 +3046,7 @@
       <c r="N56" s="2">
         <v>12</v>
       </c>
-      <c r="O56" s="2">
+      <c r="O56" s="27">
         <v>10</v>
       </c>
     </row>
@@ -3015,7 +3087,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" s="17"/>
-      <c r="O57" s="17"/>
+      <c r="O57" s="29"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
@@ -3054,7 +3126,7 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
-      <c r="O58" s="3"/>
+      <c r="O58" s="25"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
@@ -3093,7 +3165,7 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
-      <c r="O59" s="4"/>
+      <c r="O59" s="26"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
@@ -3128,7 +3200,7 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
-      <c r="O60" s="3"/>
+      <c r="O60" s="25"/>
     </row>
     <row r="61" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9">
@@ -3173,7 +3245,7 @@
       <c r="N61" s="2">
         <v>11</v>
       </c>
-      <c r="O61" s="2">
+      <c r="O61" s="27">
         <v>6</v>
       </c>
     </row>
@@ -3220,7 +3292,7 @@
       <c r="N62" s="1">
         <v>11</v>
       </c>
-      <c r="O62" s="1">
+      <c r="O62" s="24">
         <v>8</v>
       </c>
     </row>
@@ -3261,7 +3333,7 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
-      <c r="O63" s="3"/>
+      <c r="O63" s="25"/>
     </row>
     <row r="64" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="7">
@@ -3296,7 +3368,7 @@
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
-      <c r="O64" s="4"/>
+      <c r="O64" s="26"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
@@ -3335,7 +3407,7 @@
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
+      <c r="O65" s="24"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
@@ -3380,7 +3452,7 @@
       <c r="N66" s="3">
         <v>8</v>
       </c>
-      <c r="O66" s="3">
+      <c r="O66" s="25">
         <v>11</v>
       </c>
     </row>
@@ -3427,7 +3499,7 @@
       <c r="N67" s="18">
         <v>11</v>
       </c>
-      <c r="O67" s="18">
+      <c r="O67" s="30">
         <v>9</v>
       </c>
     </row>
@@ -3468,7 +3540,7 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
-      <c r="O68" s="3"/>
+      <c r="O68" s="25"/>
     </row>
     <row r="69" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9">
@@ -3503,7 +3575,7 @@
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
-      <c r="O69" s="2"/>
+      <c r="O69" s="27"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
@@ -3546,7 +3618,7 @@
         <v>4</v>
       </c>
       <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
+      <c r="O70" s="24"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
@@ -3585,7 +3657,7 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
-      <c r="O71" s="3"/>
+      <c r="O71" s="25"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
@@ -3624,7 +3696,7 @@
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
-      <c r="O72" s="4"/>
+      <c r="O72" s="26"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
@@ -3659,7 +3731,7 @@
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
-      <c r="O73" s="3"/>
+      <c r="O73" s="25"/>
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9">
@@ -3694,7 +3766,7 @@
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+      <c r="O74" s="27"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
@@ -3733,7 +3805,7 @@
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
-      <c r="O75" s="1"/>
+      <c r="O75" s="24"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
@@ -3776,7 +3848,7 @@
         <v>11</v>
       </c>
       <c r="N76" s="3"/>
-      <c r="O76" s="3"/>
+      <c r="O76" s="25"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
@@ -3815,7 +3887,7 @@
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
-      <c r="O77" s="4"/>
+      <c r="O77" s="26"/>
     </row>
     <row r="78" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="7">
@@ -3854,7 +3926,7 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
-      <c r="O78" s="3"/>
+      <c r="O78" s="25"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
@@ -3893,7 +3965,7 @@
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
-      <c r="O79" s="1"/>
+      <c r="O79" s="24"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
@@ -3936,7 +4008,7 @@
         <v>5</v>
       </c>
       <c r="N80" s="3"/>
-      <c r="O80" s="3"/>
+      <c r="O80" s="25"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
@@ -3975,7 +4047,7 @@
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
-      <c r="O81" s="4"/>
+      <c r="O81" s="26"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
@@ -4010,7 +4082,7 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-      <c r="O82" s="3"/>
+      <c r="O82" s="25"/>
     </row>
     <row r="83" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9">
@@ -4045,7 +4117,7 @@
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+      <c r="O83" s="27"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
@@ -4084,7 +4156,7 @@
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
-      <c r="O84" s="4"/>
+      <c r="O84" s="26"/>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
@@ -4119,7 +4191,7 @@
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
-      <c r="O85" s="3"/>
+      <c r="O85" s="25"/>
     </row>
     <row r="86" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="9">
@@ -4154,7 +4226,7 @@
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+      <c r="O86" s="27"/>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
@@ -4197,7 +4269,7 @@
         <v>11</v>
       </c>
       <c r="N87" s="1"/>
-      <c r="O87" s="1"/>
+      <c r="O87" s="24"/>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
@@ -4236,7 +4308,7 @@
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
-      <c r="O88" s="3"/>
+      <c r="O88" s="25"/>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
@@ -4279,7 +4351,7 @@
         <v>9</v>
       </c>
       <c r="N89" s="4"/>
-      <c r="O89" s="4"/>
+      <c r="O89" s="26"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
@@ -4314,7 +4386,7 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-      <c r="O90" s="3"/>
+      <c r="O90" s="25"/>
     </row>
     <row r="91" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9">
@@ -4357,7 +4429,7 @@
         <v>10</v>
       </c>
       <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
+      <c r="O91" s="27"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
@@ -4384,7 +4456,7 @@
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" s="17"/>
-      <c r="O92" s="17"/>
+      <c r="O92" s="29"/>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
@@ -4427,7 +4499,7 @@
         <v>11</v>
       </c>
       <c r="N93" s="3"/>
-      <c r="O93" s="3"/>
+      <c r="O93" s="25"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="7">
@@ -4462,7 +4534,7 @@
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
       <c r="N94" s="4"/>
-      <c r="O94" s="4"/>
+      <c r="O94" s="26"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="7">
@@ -4501,7 +4573,7 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-      <c r="O95" s="3"/>
+      <c r="O95" s="25"/>
     </row>
     <row r="96" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="9">
@@ -4540,7 +4612,7 @@
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+      <c r="O96" s="27"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
@@ -4585,7 +4657,7 @@
       <c r="N97" s="1">
         <v>11</v>
       </c>
-      <c r="O97" s="1">
+      <c r="O97" s="24">
         <v>8</v>
       </c>
     </row>
@@ -4622,7 +4694,7 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
       <c r="N98" s="3"/>
-      <c r="O98" s="3"/>
+      <c r="O98" s="25"/>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="7">
@@ -4667,7 +4739,7 @@
       <c r="N99" s="4">
         <v>7</v>
       </c>
-      <c r="O99" s="4">
+      <c r="O99" s="26">
         <v>11</v>
       </c>
     </row>
@@ -4708,7 +4780,7 @@
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
-      <c r="O100" s="2"/>
+      <c r="O100" s="27"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
@@ -4747,7 +4819,7 @@
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
-      <c r="O101" s="1"/>
+      <c r="O101" s="24"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="7">
@@ -4786,7 +4858,7 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
-      <c r="O102" s="3"/>
+      <c r="O102" s="25"/>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="7">
@@ -4825,7 +4897,7 @@
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
       <c r="N103" s="4"/>
-      <c r="O103" s="4"/>
+      <c r="O103" s="26"/>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="7">
@@ -4864,7 +4936,7 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
-      <c r="O104" s="3"/>
+      <c r="O104" s="25"/>
     </row>
     <row r="105" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="9">
@@ -4899,7 +4971,7 @@
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
-      <c r="O105" s="2"/>
+      <c r="O105" s="27"/>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
@@ -4926,7 +4998,7 @@
       <c r="L106" s="18"/>
       <c r="M106" s="18"/>
       <c r="N106" s="18"/>
-      <c r="O106" s="18"/>
+      <c r="O106" s="30"/>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="7">
@@ -4969,7 +5041,7 @@
         <v>12</v>
       </c>
       <c r="N107" s="3"/>
-      <c r="O107" s="3"/>
+      <c r="O107" s="25"/>
     </row>
     <row r="108" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="9">
@@ -5004,7 +5076,7 @@
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+      <c r="O108" s="27"/>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
@@ -5039,7 +5111,7 @@
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
       <c r="N109" s="1"/>
-      <c r="O109" s="1"/>
+      <c r="O109" s="24"/>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
@@ -5082,7 +5154,7 @@
         <v>11</v>
       </c>
       <c r="N110" s="3"/>
-      <c r="O110" s="3"/>
+      <c r="O110" s="25"/>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="7">
@@ -5121,7 +5193,7 @@
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
       <c r="N111" s="4"/>
-      <c r="O111" s="4"/>
+      <c r="O111" s="26"/>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="7">
@@ -5166,7 +5238,7 @@
       <c r="N112" s="3">
         <v>9</v>
       </c>
-      <c r="O112" s="3">
+      <c r="O112" s="25">
         <v>11</v>
       </c>
     </row>
@@ -5203,7 +5275,7 @@
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
+      <c r="O113" s="27"/>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
@@ -5248,7 +5320,7 @@
       <c r="N114" s="1">
         <v>11</v>
       </c>
-      <c r="O114" s="1">
+      <c r="O114" s="24">
         <v>7</v>
       </c>
     </row>
@@ -5277,7 +5349,7 @@
       <c r="L115" s="22"/>
       <c r="M115" s="22"/>
       <c r="N115" s="22"/>
-      <c r="O115" s="22"/>
+      <c r="O115" s="31"/>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
@@ -5316,7 +5388,7 @@
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
       <c r="N116" s="4"/>
-      <c r="O116" s="4"/>
+      <c r="O116" s="26"/>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="7">
@@ -5355,7 +5427,7 @@
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
       <c r="N117" s="3"/>
-      <c r="O117" s="3"/>
+      <c r="O117" s="25"/>
     </row>
     <row r="118" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="9">
@@ -5394,7 +5466,7 @@
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
+      <c r="O118" s="27"/>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="7">
@@ -5439,7 +5511,7 @@
       <c r="N119" s="3">
         <v>14</v>
       </c>
-      <c r="O119" s="3">
+      <c r="O119" s="25">
         <v>12</v>
       </c>
     </row>
@@ -5476,7 +5548,7 @@
       <c r="L120" s="4"/>
       <c r="M120" s="4"/>
       <c r="N120" s="4"/>
-      <c r="O120" s="4"/>
+      <c r="O120" s="26"/>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="7">
@@ -5511,7 +5583,7 @@
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
       <c r="N121" s="3"/>
-      <c r="O121" s="3"/>
+      <c r="O121" s="25"/>
     </row>
     <row r="122" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="9">
@@ -5550,7 +5622,7 @@
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
+      <c r="O122" s="27"/>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
@@ -5577,7 +5649,7 @@
       <c r="L123" s="23"/>
       <c r="M123" s="23"/>
       <c r="N123" s="23"/>
-      <c r="O123" s="23"/>
+      <c r="O123" s="32"/>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="7">
@@ -5595,16 +5667,32 @@
       <c r="E124" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F124" s="22"/>
-      <c r="G124" s="22"/>
-      <c r="H124" s="22"/>
-      <c r="I124" s="22"/>
-      <c r="J124" s="22"/>
-      <c r="K124" s="22"/>
-      <c r="L124" s="22"/>
-      <c r="M124" s="22"/>
-      <c r="N124" s="22"/>
-      <c r="O124" s="22"/>
+      <c r="F124" s="3">
+        <v>9</v>
+      </c>
+      <c r="G124" s="3">
+        <v>11</v>
+      </c>
+      <c r="H124" s="3">
+        <v>9</v>
+      </c>
+      <c r="I124" s="3">
+        <v>11</v>
+      </c>
+      <c r="J124" s="3">
+        <v>11</v>
+      </c>
+      <c r="K124" s="3">
+        <v>4</v>
+      </c>
+      <c r="L124" s="3">
+        <v>7</v>
+      </c>
+      <c r="M124" s="3">
+        <v>11</v>
+      </c>
+      <c r="N124" s="3"/>
+      <c r="O124" s="25"/>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="7">
@@ -5639,7 +5727,7 @@
       <c r="L125" s="4"/>
       <c r="M125" s="4"/>
       <c r="N125" s="4"/>
-      <c r="O125" s="4"/>
+      <c r="O125" s="26"/>
     </row>
     <row r="126" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="7">
@@ -5674,7 +5762,7 @@
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
       <c r="N126" s="3"/>
-      <c r="O126" s="3"/>
+      <c r="O126" s="25"/>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
@@ -5701,7 +5789,7 @@
       <c r="L127" s="17"/>
       <c r="M127" s="17"/>
       <c r="N127" s="17"/>
-      <c r="O127" s="17"/>
+      <c r="O127" s="29"/>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="7">
@@ -5719,16 +5807,28 @@
       <c r="E128" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F128" s="3"/>
-      <c r="G128" s="3"/>
-      <c r="H128" s="3"/>
-      <c r="I128" s="3"/>
-      <c r="J128" s="3"/>
-      <c r="K128" s="3"/>
+      <c r="F128" s="3">
+        <v>10</v>
+      </c>
+      <c r="G128" s="3">
+        <v>12</v>
+      </c>
+      <c r="H128" s="3">
+        <v>6</v>
+      </c>
+      <c r="I128" s="3">
+        <v>11</v>
+      </c>
+      <c r="J128" s="3">
+        <v>8</v>
+      </c>
+      <c r="K128" s="3">
+        <v>11</v>
+      </c>
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
       <c r="N128" s="3"/>
-      <c r="O128" s="3"/>
+      <c r="O128" s="25"/>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="7">
@@ -5746,16 +5846,36 @@
       <c r="E129" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F129" s="3"/>
-      <c r="G129" s="3"/>
-      <c r="H129" s="3"/>
-      <c r="I129" s="3"/>
-      <c r="J129" s="3"/>
-      <c r="K129" s="3"/>
-      <c r="L129" s="3"/>
-      <c r="M129" s="3"/>
-      <c r="N129" s="3"/>
-      <c r="O129" s="3"/>
+      <c r="F129" s="3">
+        <v>6</v>
+      </c>
+      <c r="G129" s="3">
+        <v>11</v>
+      </c>
+      <c r="H129" s="3">
+        <v>13</v>
+      </c>
+      <c r="I129" s="3">
+        <v>15</v>
+      </c>
+      <c r="J129" s="3">
+        <v>14</v>
+      </c>
+      <c r="K129" s="3">
+        <v>12</v>
+      </c>
+      <c r="L129" s="3">
+        <v>11</v>
+      </c>
+      <c r="M129" s="3">
+        <v>7</v>
+      </c>
+      <c r="N129" s="3">
+        <v>11</v>
+      </c>
+      <c r="O129" s="25">
+        <v>5</v>
+      </c>
     </row>
     <row r="130" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A130" s="9">
@@ -5773,16 +5893,28 @@
       <c r="E130" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="F130" s="2"/>
-      <c r="G130" s="2"/>
-      <c r="H130" s="2"/>
-      <c r="I130" s="2"/>
-      <c r="J130" s="2"/>
-      <c r="K130" s="2"/>
+      <c r="F130" s="2">
+        <v>4</v>
+      </c>
+      <c r="G130" s="2">
+        <v>11</v>
+      </c>
+      <c r="H130" s="2">
+        <v>6</v>
+      </c>
+      <c r="I130" s="2">
+        <v>11</v>
+      </c>
+      <c r="J130" s="2">
+        <v>8</v>
+      </c>
+      <c r="K130" s="2">
+        <v>11</v>
+      </c>
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
+      <c r="O130" s="27"/>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
@@ -5809,7 +5941,7 @@
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
       <c r="N131" s="1"/>
-      <c r="O131" s="1"/>
+      <c r="O131" s="24"/>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="7">
@@ -5836,7 +5968,7 @@
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
       <c r="N132" s="3"/>
-      <c r="O132" s="3"/>
+      <c r="O132" s="25"/>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="7">
@@ -5863,7 +5995,7 @@
       <c r="L133" s="4"/>
       <c r="M133" s="4"/>
       <c r="N133" s="4"/>
-      <c r="O133" s="4"/>
+      <c r="O133" s="26"/>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="7">
@@ -5881,16 +6013,28 @@
       <c r="E134" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F134" s="3"/>
-      <c r="G134" s="3"/>
-      <c r="H134" s="3"/>
-      <c r="I134" s="3"/>
-      <c r="J134" s="3"/>
-      <c r="K134" s="3"/>
+      <c r="F134" s="3">
+        <v>11</v>
+      </c>
+      <c r="G134" s="3">
+        <v>4</v>
+      </c>
+      <c r="H134" s="3">
+        <v>11</v>
+      </c>
+      <c r="I134" s="3">
+        <v>4</v>
+      </c>
+      <c r="J134" s="3">
+        <v>11</v>
+      </c>
+      <c r="K134" s="3">
+        <v>4</v>
+      </c>
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
       <c r="N134" s="3"/>
-      <c r="O134" s="3"/>
+      <c r="O134" s="25"/>
     </row>
     <row r="135" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="9">
@@ -5917,7 +6061,7 @@
       <c r="L135" s="2"/>
       <c r="M135" s="2"/>
       <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
+      <c r="O135" s="27"/>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
@@ -5944,7 +6088,7 @@
       <c r="L136" s="1"/>
       <c r="M136" s="1"/>
       <c r="N136" s="1"/>
-      <c r="O136" s="1"/>
+      <c r="O136" s="24"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="7">
@@ -5987,7 +6131,7 @@
         <v>11</v>
       </c>
       <c r="N137" s="3"/>
-      <c r="O137" s="3"/>
+      <c r="O137" s="25"/>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="7">
@@ -6014,7 +6158,7 @@
       <c r="L138" s="4"/>
       <c r="M138" s="4"/>
       <c r="N138" s="4"/>
-      <c r="O138" s="4"/>
+      <c r="O138" s="26"/>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="7">
@@ -6041,7 +6185,7 @@
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
       <c r="N139" s="3"/>
-      <c r="O139" s="3"/>
+      <c r="O139" s="25"/>
     </row>
     <row r="140" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="9">
@@ -6068,7 +6212,7 @@
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
+      <c r="O140" s="27"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
@@ -6095,7 +6239,7 @@
       <c r="L141" s="17"/>
       <c r="M141" s="17"/>
       <c r="N141" s="17"/>
-      <c r="O141" s="17"/>
+      <c r="O141" s="29"/>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="7">
@@ -6122,7 +6266,7 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3"/>
-      <c r="O142" s="3"/>
+      <c r="O142" s="25"/>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="7">
@@ -6149,7 +6293,7 @@
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
-      <c r="O143" s="4"/>
+      <c r="O143" s="26"/>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="7">
@@ -6176,7 +6320,7 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
       <c r="N144" s="3"/>
-      <c r="O144" s="3"/>
+      <c r="O144" s="25"/>
     </row>
     <row r="145" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="9">
@@ -6203,7 +6347,7 @@
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
-      <c r="O145" s="2"/>
+      <c r="O145" s="27"/>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
@@ -6230,7 +6374,7 @@
       <c r="L146" s="1"/>
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>
-      <c r="O146" s="1"/>
+      <c r="O146" s="24"/>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="7">
@@ -6257,7 +6401,7 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
       <c r="N147" s="3"/>
-      <c r="O147" s="3"/>
+      <c r="O147" s="25"/>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="7">
@@ -6284,7 +6428,7 @@
       <c r="L148" s="4"/>
       <c r="M148" s="4"/>
       <c r="N148" s="4"/>
-      <c r="O148" s="4"/>
+      <c r="O148" s="26"/>
     </row>
     <row r="149" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="7">
@@ -6311,7 +6455,7 @@
       <c r="L149" s="3"/>
       <c r="M149" s="3"/>
       <c r="N149" s="3"/>
-      <c r="O149" s="3"/>
+      <c r="O149" s="25"/>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
@@ -6338,7 +6482,7 @@
       <c r="L150" s="1"/>
       <c r="M150" s="1"/>
       <c r="N150" s="1"/>
-      <c r="O150" s="1"/>
+      <c r="O150" s="24"/>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="7">
@@ -6365,7 +6509,7 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
       <c r="N151" s="3"/>
-      <c r="O151" s="3"/>
+      <c r="O151" s="25"/>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="7">
@@ -6392,7 +6536,7 @@
       <c r="L152" s="4"/>
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
-      <c r="O152" s="4"/>
+      <c r="O152" s="26"/>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="7">
@@ -6419,7 +6563,7 @@
       <c r="L153" s="3"/>
       <c r="M153" s="3"/>
       <c r="N153" s="3"/>
-      <c r="O153" s="3"/>
+      <c r="O153" s="25"/>
     </row>
     <row r="154" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="9">
@@ -6446,7 +6590,7 @@
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
-      <c r="O154" s="2"/>
+      <c r="O154" s="27"/>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="7">
@@ -6473,7 +6617,7 @@
       <c r="L155" s="3"/>
       <c r="M155" s="3"/>
       <c r="N155" s="3"/>
-      <c r="O155" s="3"/>
+      <c r="O155" s="25"/>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="7">
@@ -6500,7 +6644,7 @@
       <c r="L156" s="4"/>
       <c r="M156" s="4"/>
       <c r="N156" s="4"/>
-      <c r="O156" s="4"/>
+      <c r="O156" s="26"/>
     </row>
     <row r="157" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="9">
@@ -6527,7 +6671,7 @@
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
-      <c r="O157" s="2"/>
+      <c r="O157" s="27"/>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="7">
@@ -6554,7 +6698,7 @@
       <c r="L158" s="3"/>
       <c r="M158" s="3"/>
       <c r="N158" s="3"/>
-      <c r="O158" s="3"/>
+      <c r="O158" s="25"/>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="7">
@@ -6581,7 +6725,7 @@
       <c r="L159" s="4"/>
       <c r="M159" s="4"/>
       <c r="N159" s="4"/>
-      <c r="O159" s="4"/>
+      <c r="O159" s="26"/>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="7">
@@ -6608,7 +6752,7 @@
       <c r="L160" s="3"/>
       <c r="M160" s="3"/>
       <c r="N160" s="3"/>
-      <c r="O160" s="3"/>
+      <c r="O160" s="25"/>
     </row>
     <row r="161" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="9">
@@ -6635,7 +6779,7 @@
       <c r="L161" s="16"/>
       <c r="M161" s="16"/>
       <c r="N161" s="16"/>
-      <c r="O161" s="16"/>
+      <c r="O161" s="28"/>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
@@ -6662,7 +6806,7 @@
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
       <c r="N162" s="1"/>
-      <c r="O162" s="1"/>
+      <c r="O162" s="24"/>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="7">
@@ -6689,7 +6833,7 @@
       <c r="L163" s="3"/>
       <c r="M163" s="3"/>
       <c r="N163" s="3"/>
-      <c r="O163" s="3"/>
+      <c r="O163" s="25"/>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="7">
@@ -6716,7 +6860,7 @@
       <c r="L164" s="4"/>
       <c r="M164" s="4"/>
       <c r="N164" s="4"/>
-      <c r="O164" s="4"/>
+      <c r="O164" s="26"/>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="7">
@@ -6743,7 +6887,7 @@
       <c r="L165" s="3"/>
       <c r="M165" s="3"/>
       <c r="N165" s="3"/>
-      <c r="O165" s="3"/>
+      <c r="O165" s="25"/>
     </row>
     <row r="166" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="9">
@@ -6770,7 +6914,7 @@
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
-      <c r="O166" s="2"/>
+      <c r="O166" s="27"/>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
@@ -6797,7 +6941,7 @@
       <c r="L167" s="1"/>
       <c r="M167" s="1"/>
       <c r="N167" s="1"/>
-      <c r="O167" s="1"/>
+      <c r="O167" s="24"/>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="7">
@@ -6824,7 +6968,7 @@
       <c r="L168" s="4"/>
       <c r="M168" s="4"/>
       <c r="N168" s="4"/>
-      <c r="O168" s="4"/>
+      <c r="O168" s="26"/>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="7">
@@ -6851,7 +6995,7 @@
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
       <c r="N169" s="3"/>
-      <c r="O169" s="3"/>
+      <c r="O169" s="25"/>
     </row>
     <row r="170" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="9">
@@ -6878,7 +7022,7 @@
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
-      <c r="O170" s="2"/>
+      <c r="O170" s="27"/>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
@@ -6905,7 +7049,7 @@
       <c r="L171" s="1"/>
       <c r="M171" s="1"/>
       <c r="N171" s="1"/>
-      <c r="O171" s="1"/>
+      <c r="O171" s="24"/>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="7">
@@ -6932,7 +7076,7 @@
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
       <c r="N172" s="3"/>
-      <c r="O172" s="3"/>
+      <c r="O172" s="25"/>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="7">
@@ -6959,34 +7103,34 @@
       <c r="L173" s="4"/>
       <c r="M173" s="4"/>
       <c r="N173" s="4"/>
-      <c r="O173" s="4"/>
-    </row>
-    <row r="174" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A174" s="7">
+      <c r="O173" s="26"/>
+    </row>
+    <row r="174" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A174" s="9">
         <v>46107</v>
       </c>
-      <c r="B174" s="8">
-        <v>0.59722222222222221</v>
-      </c>
-      <c r="C174" s="13">
+      <c r="B174" s="10">
+        <v>0.59722222222222221</v>
+      </c>
+      <c r="C174" s="14">
         <v>199</v>
       </c>
-      <c r="D174" s="3" t="s">
+      <c r="D174" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E174" s="3" t="s">
+      <c r="E174" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F174" s="3"/>
-      <c r="G174" s="3"/>
-      <c r="H174" s="3"/>
-      <c r="I174" s="3"/>
-      <c r="J174" s="3"/>
-      <c r="K174" s="3"/>
-      <c r="L174" s="3"/>
-      <c r="M174" s="3"/>
-      <c r="N174" s="3"/>
-      <c r="O174" s="3"/>
+      <c r="F174" s="2"/>
+      <c r="G174" s="2"/>
+      <c r="H174" s="2"/>
+      <c r="I174" s="2"/>
+      <c r="J174" s="2"/>
+      <c r="K174" s="2"/>
+      <c r="L174" s="2"/>
+      <c r="M174" s="2"/>
+      <c r="N174" s="2"/>
+      <c r="O174" s="27"/>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B175" s="12"/>

--- a/RESULTADOS T6.xlsx
+++ b/RESULTADOS T6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235F652D-1B29-4AFF-BD3C-C52C5EBBAEFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954073BE-7BC1-49E2-8617-44D2CB007BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -227,7 +227,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -330,58 +330,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -445,34 +400,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -818,32 +746,32 @@
       <c r="E1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1">
-        <v>11</v>
-      </c>
-      <c r="G1" s="1">
+      <c r="F1" s="3">
+        <v>11</v>
+      </c>
+      <c r="G1" s="3">
         <v>8</v>
       </c>
-      <c r="H1" s="1">
+      <c r="H1" s="3">
         <v>4</v>
       </c>
-      <c r="I1" s="1">
-        <v>11</v>
-      </c>
-      <c r="J1" s="1">
+      <c r="I1" s="3">
+        <v>11</v>
+      </c>
+      <c r="J1" s="3">
         <v>10</v>
       </c>
-      <c r="K1" s="1">
+      <c r="K1" s="3">
         <v>12</v>
       </c>
-      <c r="L1" s="1">
+      <c r="L1" s="3">
         <v>5</v>
       </c>
-      <c r="M1" s="1">
-        <v>11</v>
-      </c>
-      <c r="N1" s="1"/>
-      <c r="O1" s="24"/>
+      <c r="M1" s="3">
+        <v>11</v>
+      </c>
+      <c r="N1" s="3"/>
+      <c r="O1" s="3"/>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
@@ -886,7 +814,7 @@
         <v>11</v>
       </c>
       <c r="N2" s="4"/>
-      <c r="O2" s="26"/>
+      <c r="O2" s="4"/>
     </row>
     <row r="3" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7">
@@ -921,7 +849,7 @@
       <c r="L3" s="3"/>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
-      <c r="O3" s="25"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
@@ -964,7 +892,7 @@
         <v>10</v>
       </c>
       <c r="N4" s="1"/>
-      <c r="O4" s="24"/>
+      <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A5" s="7">
@@ -1003,7 +931,7 @@
       <c r="L5" s="3"/>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
-      <c r="O5" s="25"/>
+      <c r="O5" s="3"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A6" s="7">
@@ -1038,7 +966,7 @@
       <c r="L6" s="3"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
-      <c r="O6" s="25"/>
+      <c r="O6" s="3"/>
     </row>
     <row r="7" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
@@ -1073,7 +1001,7 @@
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
-      <c r="O7" s="27"/>
+      <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="5">
@@ -1112,7 +1040,7 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
       <c r="N8" s="1"/>
-      <c r="O8" s="24"/>
+      <c r="O8" s="1"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="7">
@@ -1157,7 +1085,7 @@
       <c r="N9" s="3">
         <v>3</v>
       </c>
-      <c r="O9" s="25">
+      <c r="O9" s="3">
         <v>11</v>
       </c>
     </row>
@@ -1198,7 +1126,7 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
-      <c r="O10" s="26"/>
+      <c r="O10" s="4"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A11" s="7">
@@ -1233,7 +1161,7 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-      <c r="O11" s="25"/>
+      <c r="O11" s="3"/>
     </row>
     <row r="12" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
@@ -1272,7 +1200,7 @@
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="27"/>
+      <c r="O12" s="2"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
@@ -1317,7 +1245,7 @@
       <c r="N13" s="1">
         <v>15</v>
       </c>
-      <c r="O13" s="24">
+      <c r="O13" s="1">
         <v>13</v>
       </c>
     </row>
@@ -1362,7 +1290,7 @@
         <v>11</v>
       </c>
       <c r="N14" s="3"/>
-      <c r="O14" s="25"/>
+      <c r="O14" s="3"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="7">
@@ -1401,7 +1329,7 @@
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4"/>
-      <c r="O15" s="26"/>
+      <c r="O15" s="4"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A16" s="7">
@@ -1436,7 +1364,7 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-      <c r="O16" s="25"/>
+      <c r="O16" s="3"/>
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="9">
@@ -1471,7 +1399,7 @@
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
-      <c r="O17" s="27"/>
+      <c r="O17" s="2"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
@@ -1510,7 +1438,7 @@
       <c r="L18" s="1"/>
       <c r="M18" s="1"/>
       <c r="N18" s="1"/>
-      <c r="O18" s="24"/>
+      <c r="O18" s="1"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="7">
@@ -1549,7 +1477,7 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-      <c r="O19" s="25"/>
+      <c r="O19" s="3"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
@@ -1588,7 +1516,7 @@
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4"/>
-      <c r="O20" s="26"/>
+      <c r="O20" s="4"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A21" s="7">
@@ -1623,7 +1551,7 @@
       <c r="L21" s="3"/>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
-      <c r="O21" s="25"/>
+      <c r="O21" s="3"/>
     </row>
     <row r="22" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A22" s="9">
@@ -1668,7 +1596,7 @@
       <c r="N22" s="2">
         <v>11</v>
       </c>
-      <c r="O22" s="27">
+      <c r="O22" s="2">
         <v>7</v>
       </c>
     </row>
@@ -1709,7 +1637,7 @@
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
-      <c r="O23" s="24"/>
+      <c r="O23" s="1"/>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A24" s="7">
@@ -1748,7 +1676,7 @@
       <c r="L24" s="3"/>
       <c r="M24" s="3"/>
       <c r="N24" s="3"/>
-      <c r="O24" s="25"/>
+      <c r="O24" s="3"/>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A25" s="7">
@@ -1783,7 +1711,7 @@
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
       <c r="N25" s="4"/>
-      <c r="O25" s="26"/>
+      <c r="O25" s="4"/>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="7">
@@ -1822,7 +1750,7 @@
       <c r="L26" s="3"/>
       <c r="M26" s="3"/>
       <c r="N26" s="3"/>
-      <c r="O26" s="25"/>
+      <c r="O26" s="3"/>
     </row>
     <row r="27" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A27" s="9">
@@ -1865,7 +1793,7 @@
         <v>11</v>
       </c>
       <c r="N27" s="16"/>
-      <c r="O27" s="28"/>
+      <c r="O27" s="16"/>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
@@ -1910,7 +1838,7 @@
       <c r="N28" s="1">
         <v>11</v>
       </c>
-      <c r="O28" s="24">
+      <c r="O28" s="1">
         <v>7</v>
       </c>
     </row>
@@ -1957,7 +1885,7 @@
       <c r="N29" s="4">
         <v>2</v>
       </c>
-      <c r="O29" s="26">
+      <c r="O29" s="4">
         <v>11</v>
       </c>
     </row>
@@ -1998,7 +1926,7 @@
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="2"/>
-      <c r="O30" s="27"/>
+      <c r="O30" s="2"/>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
@@ -2033,7 +1961,7 @@
       <c r="L31" s="1"/>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
-      <c r="O31" s="24"/>
+      <c r="O31" s="1"/>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A32" s="7">
@@ -2076,7 +2004,7 @@
         <v>11</v>
       </c>
       <c r="N32" s="3"/>
-      <c r="O32" s="25"/>
+      <c r="O32" s="3"/>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A33" s="7">
@@ -2115,7 +2043,7 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4"/>
-      <c r="O33" s="26"/>
+      <c r="O33" s="4"/>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="7">
@@ -2154,7 +2082,7 @@
       <c r="L34" s="3"/>
       <c r="M34" s="3"/>
       <c r="N34" s="3"/>
-      <c r="O34" s="25"/>
+      <c r="O34" s="3"/>
     </row>
     <row r="35" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A35" s="9">
@@ -2189,7 +2117,7 @@
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
-      <c r="O35" s="27"/>
+      <c r="O35" s="2"/>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
@@ -2224,7 +2152,7 @@
       <c r="L36" s="1"/>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
-      <c r="O36" s="24"/>
+      <c r="O36" s="1"/>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A37" s="7">
@@ -2267,7 +2195,7 @@
         <v>5</v>
       </c>
       <c r="N37" s="4"/>
-      <c r="O37" s="26"/>
+      <c r="O37" s="4"/>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A38" s="7">
@@ -2310,7 +2238,7 @@
         <v>11</v>
       </c>
       <c r="N38" s="3"/>
-      <c r="O38" s="25"/>
+      <c r="O38" s="3"/>
     </row>
     <row r="39" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A39" s="9">
@@ -2345,7 +2273,7 @@
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
-      <c r="O39" s="27"/>
+      <c r="O39" s="2"/>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
@@ -2380,7 +2308,7 @@
       <c r="L40" s="1"/>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
-      <c r="O40" s="24"/>
+      <c r="O40" s="1"/>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A41" s="7">
@@ -2425,7 +2353,7 @@
       <c r="N41" s="4">
         <v>6</v>
       </c>
-      <c r="O41" s="26">
+      <c r="O41" s="4">
         <v>11</v>
       </c>
     </row>
@@ -2470,7 +2398,7 @@
         <v>9</v>
       </c>
       <c r="N42" s="3"/>
-      <c r="O42" s="25"/>
+      <c r="O42" s="3"/>
     </row>
     <row r="43" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A43" s="9">
@@ -2509,7 +2437,7 @@
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
-      <c r="O43" s="27"/>
+      <c r="O43" s="2"/>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
@@ -2554,7 +2482,7 @@
       <c r="N44" s="1">
         <v>11</v>
       </c>
-      <c r="O44" s="24">
+      <c r="O44" s="1">
         <v>3</v>
       </c>
     </row>
@@ -2599,7 +2527,7 @@
         <v>10</v>
       </c>
       <c r="N45" s="3"/>
-      <c r="O45" s="25"/>
+      <c r="O45" s="3"/>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="7">
@@ -2638,7 +2566,7 @@
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4"/>
-      <c r="O46" s="26"/>
+      <c r="O46" s="4"/>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="7">
@@ -2677,7 +2605,7 @@
       <c r="L47" s="3"/>
       <c r="M47" s="3"/>
       <c r="N47" s="3"/>
-      <c r="O47" s="25"/>
+      <c r="O47" s="3"/>
     </row>
     <row r="48" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A48" s="9">
@@ -2722,7 +2650,7 @@
       <c r="N48" s="2">
         <v>11</v>
       </c>
-      <c r="O48" s="27">
+      <c r="O48" s="2">
         <v>7</v>
       </c>
     </row>
@@ -2763,7 +2691,7 @@
       <c r="L49" s="1"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
-      <c r="O49" s="24"/>
+      <c r="O49" s="1"/>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="7">
@@ -2802,7 +2730,7 @@
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
       <c r="N50" s="3"/>
-      <c r="O50" s="25"/>
+      <c r="O50" s="3"/>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A51" s="7">
@@ -2841,7 +2769,7 @@
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
       <c r="N51" s="4"/>
-      <c r="O51" s="26"/>
+      <c r="O51" s="4"/>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="7">
@@ -2876,7 +2804,7 @@
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
       <c r="N52" s="3"/>
-      <c r="O52" s="25"/>
+      <c r="O52" s="3"/>
     </row>
     <row r="53" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A53" s="9">
@@ -2921,7 +2849,7 @@
       <c r="N53" s="2">
         <v>4</v>
       </c>
-      <c r="O53" s="27">
+      <c r="O53" s="2">
         <v>11</v>
       </c>
     </row>
@@ -2966,7 +2894,7 @@
         <v>11</v>
       </c>
       <c r="N54" s="3"/>
-      <c r="O54" s="25"/>
+      <c r="O54" s="3"/>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A55" s="7">
@@ -3001,7 +2929,7 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4"/>
-      <c r="O55" s="26"/>
+      <c r="O55" s="4"/>
     </row>
     <row r="56" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A56" s="9">
@@ -3046,7 +2974,7 @@
       <c r="N56" s="2">
         <v>12</v>
       </c>
-      <c r="O56" s="27">
+      <c r="O56" s="2">
         <v>10</v>
       </c>
     </row>
@@ -3087,7 +3015,7 @@
       <c r="L57" s="17"/>
       <c r="M57" s="17"/>
       <c r="N57" s="17"/>
-      <c r="O57" s="29"/>
+      <c r="O57" s="17"/>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A58" s="7">
@@ -3126,7 +3054,7 @@
       <c r="L58" s="3"/>
       <c r="M58" s="3"/>
       <c r="N58" s="3"/>
-      <c r="O58" s="25"/>
+      <c r="O58" s="3"/>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="7">
@@ -3165,7 +3093,7 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4"/>
-      <c r="O59" s="26"/>
+      <c r="O59" s="4"/>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="7">
@@ -3200,7 +3128,7 @@
       <c r="L60" s="3"/>
       <c r="M60" s="3"/>
       <c r="N60" s="3"/>
-      <c r="O60" s="25"/>
+      <c r="O60" s="3"/>
     </row>
     <row r="61" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A61" s="9">
@@ -3245,7 +3173,7 @@
       <c r="N61" s="2">
         <v>11</v>
       </c>
-      <c r="O61" s="27">
+      <c r="O61" s="2">
         <v>6</v>
       </c>
     </row>
@@ -3292,7 +3220,7 @@
       <c r="N62" s="1">
         <v>11</v>
       </c>
-      <c r="O62" s="24">
+      <c r="O62" s="1">
         <v>8</v>
       </c>
     </row>
@@ -3333,7 +3261,7 @@
       <c r="L63" s="3"/>
       <c r="M63" s="3"/>
       <c r="N63" s="3"/>
-      <c r="O63" s="25"/>
+      <c r="O63" s="3"/>
     </row>
     <row r="64" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A64" s="7">
@@ -3368,7 +3296,7 @@
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
       <c r="N64" s="4"/>
-      <c r="O64" s="26"/>
+      <c r="O64" s="4"/>
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="5">
@@ -3407,7 +3335,7 @@
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
-      <c r="O65" s="24"/>
+      <c r="O65" s="1"/>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A66" s="7">
@@ -3452,7 +3380,7 @@
       <c r="N66" s="3">
         <v>8</v>
       </c>
-      <c r="O66" s="25">
+      <c r="O66" s="3">
         <v>11</v>
       </c>
     </row>
@@ -3499,7 +3427,7 @@
       <c r="N67" s="18">
         <v>11</v>
       </c>
-      <c r="O67" s="30">
+      <c r="O67" s="18">
         <v>9</v>
       </c>
     </row>
@@ -3540,7 +3468,7 @@
       <c r="L68" s="3"/>
       <c r="M68" s="3"/>
       <c r="N68" s="3"/>
-      <c r="O68" s="25"/>
+      <c r="O68" s="3"/>
     </row>
     <row r="69" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A69" s="9">
@@ -3575,7 +3503,7 @@
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
       <c r="N69" s="2"/>
-      <c r="O69" s="27"/>
+      <c r="O69" s="2"/>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A70" s="5">
@@ -3618,7 +3546,7 @@
         <v>4</v>
       </c>
       <c r="N70" s="1"/>
-      <c r="O70" s="24"/>
+      <c r="O70" s="1"/>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A71" s="7">
@@ -3657,7 +3585,7 @@
       <c r="L71" s="3"/>
       <c r="M71" s="3"/>
       <c r="N71" s="3"/>
-      <c r="O71" s="25"/>
+      <c r="O71" s="3"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A72" s="7">
@@ -3696,7 +3624,7 @@
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
       <c r="N72" s="4"/>
-      <c r="O72" s="26"/>
+      <c r="O72" s="4"/>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="7">
@@ -3731,7 +3659,7 @@
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
-      <c r="O73" s="25"/>
+      <c r="O73" s="3"/>
     </row>
     <row r="74" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A74" s="9">
@@ -3766,7 +3694,7 @@
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="2"/>
-      <c r="O74" s="27"/>
+      <c r="O74" s="2"/>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="5">
@@ -3805,7 +3733,7 @@
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
-      <c r="O75" s="24"/>
+      <c r="O75" s="1"/>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="7">
@@ -3848,7 +3776,7 @@
         <v>11</v>
       </c>
       <c r="N76" s="3"/>
-      <c r="O76" s="25"/>
+      <c r="O76" s="3"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A77" s="7">
@@ -3887,7 +3815,7 @@
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
       <c r="N77" s="4"/>
-      <c r="O77" s="26"/>
+      <c r="O77" s="4"/>
     </row>
     <row r="78" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A78" s="7">
@@ -3926,7 +3854,7 @@
       <c r="L78" s="3"/>
       <c r="M78" s="3"/>
       <c r="N78" s="3"/>
-      <c r="O78" s="25"/>
+      <c r="O78" s="3"/>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="5">
@@ -3965,7 +3893,7 @@
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
-      <c r="O79" s="24"/>
+      <c r="O79" s="1"/>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="7">
@@ -4008,7 +3936,7 @@
         <v>5</v>
       </c>
       <c r="N80" s="3"/>
-      <c r="O80" s="25"/>
+      <c r="O80" s="3"/>
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A81" s="7">
@@ -4047,7 +3975,7 @@
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4"/>
-      <c r="O81" s="26"/>
+      <c r="O81" s="4"/>
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A82" s="7">
@@ -4082,7 +4010,7 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-      <c r="O82" s="25"/>
+      <c r="O82" s="3"/>
     </row>
     <row r="83" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A83" s="9">
@@ -4117,7 +4045,7 @@
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
       <c r="N83" s="2"/>
-      <c r="O83" s="27"/>
+      <c r="O83" s="2"/>
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A84" s="7">
@@ -4156,7 +4084,7 @@
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
       <c r="N84" s="4"/>
-      <c r="O84" s="26"/>
+      <c r="O84" s="4"/>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A85" s="7">
@@ -4191,7 +4119,7 @@
       <c r="L85" s="3"/>
       <c r="M85" s="3"/>
       <c r="N85" s="3"/>
-      <c r="O85" s="25"/>
+      <c r="O85" s="3"/>
     </row>
     <row r="86" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A86" s="9">
@@ -4226,7 +4154,7 @@
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
-      <c r="O86" s="27"/>
+      <c r="O86" s="2"/>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A87" s="5">
@@ -4269,7 +4197,7 @@
         <v>11</v>
       </c>
       <c r="N87" s="1"/>
-      <c r="O87" s="24"/>
+      <c r="O87" s="1"/>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A88" s="7">
@@ -4308,7 +4236,7 @@
       <c r="L88" s="3"/>
       <c r="M88" s="3"/>
       <c r="N88" s="3"/>
-      <c r="O88" s="25"/>
+      <c r="O88" s="3"/>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A89" s="7">
@@ -4351,7 +4279,7 @@
         <v>9</v>
       </c>
       <c r="N89" s="4"/>
-      <c r="O89" s="26"/>
+      <c r="O89" s="4"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A90" s="7">
@@ -4386,7 +4314,7 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-      <c r="O90" s="25"/>
+      <c r="O90" s="3"/>
     </row>
     <row r="91" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A91" s="9">
@@ -4429,7 +4357,7 @@
         <v>10</v>
       </c>
       <c r="N91" s="2"/>
-      <c r="O91" s="27"/>
+      <c r="O91" s="2"/>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A92" s="5">
@@ -4456,7 +4384,7 @@
       <c r="L92" s="17"/>
       <c r="M92" s="17"/>
       <c r="N92" s="17"/>
-      <c r="O92" s="29"/>
+      <c r="O92" s="17"/>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A93" s="7">
@@ -4499,7 +4427,7 @@
         <v>11</v>
       </c>
       <c r="N93" s="3"/>
-      <c r="O93" s="25"/>
+      <c r="O93" s="3"/>
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A94" s="7">
@@ -4534,7 +4462,7 @@
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
       <c r="N94" s="4"/>
-      <c r="O94" s="26"/>
+      <c r="O94" s="4"/>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="7">
@@ -4573,7 +4501,7 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-      <c r="O95" s="25"/>
+      <c r="O95" s="3"/>
     </row>
     <row r="96" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A96" s="9">
@@ -4612,7 +4540,7 @@
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
-      <c r="O96" s="27"/>
+      <c r="O96" s="2"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="5">
@@ -4657,7 +4585,7 @@
       <c r="N97" s="1">
         <v>11</v>
       </c>
-      <c r="O97" s="24">
+      <c r="O97" s="1">
         <v>8</v>
       </c>
     </row>
@@ -4694,7 +4622,7 @@
       <c r="L98" s="3"/>
       <c r="M98" s="3"/>
       <c r="N98" s="3"/>
-      <c r="O98" s="25"/>
+      <c r="O98" s="3"/>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A99" s="7">
@@ -4739,7 +4667,7 @@
       <c r="N99" s="4">
         <v>7</v>
       </c>
-      <c r="O99" s="26">
+      <c r="O99" s="4">
         <v>11</v>
       </c>
     </row>
@@ -4780,7 +4708,7 @@
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
-      <c r="O100" s="27"/>
+      <c r="O100" s="2"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="5">
@@ -4819,7 +4747,7 @@
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
-      <c r="O101" s="24"/>
+      <c r="O101" s="1"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="7">
@@ -4858,7 +4786,7 @@
       <c r="L102" s="3"/>
       <c r="M102" s="3"/>
       <c r="N102" s="3"/>
-      <c r="O102" s="25"/>
+      <c r="O102" s="3"/>
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A103" s="7">
@@ -4897,7 +4825,7 @@
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
       <c r="N103" s="4"/>
-      <c r="O103" s="26"/>
+      <c r="O103" s="4"/>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A104" s="7">
@@ -4936,7 +4864,7 @@
       <c r="L104" s="3"/>
       <c r="M104" s="3"/>
       <c r="N104" s="3"/>
-      <c r="O104" s="25"/>
+      <c r="O104" s="3"/>
     </row>
     <row r="105" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A105" s="9">
@@ -4971,7 +4899,7 @@
       <c r="L105" s="2"/>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
-      <c r="O105" s="27"/>
+      <c r="O105" s="2"/>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
@@ -4998,7 +4926,7 @@
       <c r="L106" s="18"/>
       <c r="M106" s="18"/>
       <c r="N106" s="18"/>
-      <c r="O106" s="30"/>
+      <c r="O106" s="18"/>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A107" s="7">
@@ -5041,7 +4969,7 @@
         <v>12</v>
       </c>
       <c r="N107" s="3"/>
-      <c r="O107" s="25"/>
+      <c r="O107" s="3"/>
     </row>
     <row r="108" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A108" s="9">
@@ -5076,7 +5004,7 @@
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
-      <c r="O108" s="27"/>
+      <c r="O108" s="2"/>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A109" s="5">
@@ -5111,7 +5039,7 @@
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
       <c r="N109" s="1"/>
-      <c r="O109" s="24"/>
+      <c r="O109" s="1"/>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A110" s="7">
@@ -5154,7 +5082,7 @@
         <v>11</v>
       </c>
       <c r="N110" s="3"/>
-      <c r="O110" s="25"/>
+      <c r="O110" s="3"/>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A111" s="7">
@@ -5193,7 +5121,7 @@
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
       <c r="N111" s="4"/>
-      <c r="O111" s="26"/>
+      <c r="O111" s="4"/>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A112" s="7">
@@ -5238,7 +5166,7 @@
       <c r="N112" s="3">
         <v>9</v>
       </c>
-      <c r="O112" s="25">
+      <c r="O112" s="3">
         <v>11</v>
       </c>
     </row>
@@ -5275,7 +5203,7 @@
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
-      <c r="O113" s="27"/>
+      <c r="O113" s="2"/>
     </row>
     <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="5">
@@ -5320,7 +5248,7 @@
       <c r="N114" s="1">
         <v>11</v>
       </c>
-      <c r="O114" s="24">
+      <c r="O114" s="1">
         <v>7</v>
       </c>
     </row>
@@ -5349,7 +5277,7 @@
       <c r="L115" s="22"/>
       <c r="M115" s="22"/>
       <c r="N115" s="22"/>
-      <c r="O115" s="31"/>
+      <c r="O115" s="22"/>
     </row>
     <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="7">
@@ -5388,7 +5316,7 @@
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
       <c r="N116" s="4"/>
-      <c r="O116" s="26"/>
+      <c r="O116" s="4"/>
     </row>
     <row r="117" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A117" s="7">
@@ -5427,7 +5355,7 @@
       <c r="L117" s="3"/>
       <c r="M117" s="3"/>
       <c r="N117" s="3"/>
-      <c r="O117" s="25"/>
+      <c r="O117" s="3"/>
     </row>
     <row r="118" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A118" s="9">
@@ -5466,7 +5394,7 @@
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
-      <c r="O118" s="27"/>
+      <c r="O118" s="2"/>
     </row>
     <row r="119" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A119" s="7">
@@ -5511,7 +5439,7 @@
       <c r="N119" s="3">
         <v>14</v>
       </c>
-      <c r="O119" s="25">
+      <c r="O119" s="3">
         <v>12</v>
       </c>
     </row>
@@ -5548,7 +5476,7 @@
       <c r="L120" s="4"/>
       <c r="M120" s="4"/>
       <c r="N120" s="4"/>
-      <c r="O120" s="26"/>
+      <c r="O120" s="4"/>
     </row>
     <row r="121" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A121" s="7">
@@ -5583,7 +5511,7 @@
       <c r="L121" s="3"/>
       <c r="M121" s="3"/>
       <c r="N121" s="3"/>
-      <c r="O121" s="25"/>
+      <c r="O121" s="3"/>
     </row>
     <row r="122" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A122" s="9">
@@ -5622,7 +5550,7 @@
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
-      <c r="O122" s="27"/>
+      <c r="O122" s="2"/>
     </row>
     <row r="123" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A123" s="5">
@@ -5640,16 +5568,36 @@
       <c r="E123" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="F123" s="23"/>
-      <c r="G123" s="23"/>
-      <c r="H123" s="23"/>
-      <c r="I123" s="23"/>
-      <c r="J123" s="23"/>
-      <c r="K123" s="23"/>
-      <c r="L123" s="23"/>
-      <c r="M123" s="23"/>
-      <c r="N123" s="23"/>
-      <c r="O123" s="32"/>
+      <c r="F123" s="1">
+        <v>4</v>
+      </c>
+      <c r="G123" s="1">
+        <v>11</v>
+      </c>
+      <c r="H123" s="1">
+        <v>8</v>
+      </c>
+      <c r="I123" s="1">
+        <v>11</v>
+      </c>
+      <c r="J123" s="1">
+        <v>11</v>
+      </c>
+      <c r="K123" s="1">
+        <v>7</v>
+      </c>
+      <c r="L123" s="1">
+        <v>11</v>
+      </c>
+      <c r="M123" s="1">
+        <v>8</v>
+      </c>
+      <c r="N123" s="1">
+        <v>11</v>
+      </c>
+      <c r="O123" s="1">
+        <v>9</v>
+      </c>
     </row>
     <row r="124" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A124" s="7">
@@ -5692,7 +5640,7 @@
         <v>11</v>
       </c>
       <c r="N124" s="3"/>
-      <c r="O124" s="25"/>
+      <c r="O124" s="3"/>
     </row>
     <row r="125" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A125" s="7">
@@ -5727,7 +5675,7 @@
       <c r="L125" s="4"/>
       <c r="M125" s="4"/>
       <c r="N125" s="4"/>
-      <c r="O125" s="26"/>
+      <c r="O125" s="4"/>
     </row>
     <row r="126" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A126" s="7">
@@ -5762,7 +5710,7 @@
       <c r="L126" s="3"/>
       <c r="M126" s="3"/>
       <c r="N126" s="3"/>
-      <c r="O126" s="25"/>
+      <c r="O126" s="3"/>
     </row>
     <row r="127" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A127" s="5">
@@ -5789,7 +5737,7 @@
       <c r="L127" s="17"/>
       <c r="M127" s="17"/>
       <c r="N127" s="17"/>
-      <c r="O127" s="29"/>
+      <c r="O127" s="17"/>
     </row>
     <row r="128" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A128" s="7">
@@ -5828,7 +5776,7 @@
       <c r="L128" s="3"/>
       <c r="M128" s="3"/>
       <c r="N128" s="3"/>
-      <c r="O128" s="25"/>
+      <c r="O128" s="3"/>
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A129" s="7">
@@ -5873,7 +5821,7 @@
       <c r="N129" s="3">
         <v>11</v>
       </c>
-      <c r="O129" s="25">
+      <c r="O129" s="3">
         <v>5</v>
       </c>
     </row>
@@ -5914,7 +5862,7 @@
       <c r="L130" s="2"/>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
-      <c r="O130" s="27"/>
+      <c r="O130" s="2"/>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A131" s="5">
@@ -5932,16 +5880,28 @@
       <c r="E131" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F131" s="1"/>
-      <c r="G131" s="1"/>
-      <c r="H131" s="1"/>
-      <c r="I131" s="1"/>
-      <c r="J131" s="1"/>
-      <c r="K131" s="1"/>
+      <c r="F131" s="1">
+        <v>7</v>
+      </c>
+      <c r="G131" s="1">
+        <v>11</v>
+      </c>
+      <c r="H131" s="1">
+        <v>6</v>
+      </c>
+      <c r="I131" s="1">
+        <v>11</v>
+      </c>
+      <c r="J131" s="1">
+        <v>5</v>
+      </c>
+      <c r="K131" s="1">
+        <v>11</v>
+      </c>
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
       <c r="N131" s="1"/>
-      <c r="O131" s="24"/>
+      <c r="O131" s="1"/>
     </row>
     <row r="132" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A132" s="7">
@@ -5959,16 +5919,24 @@
       <c r="E132" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F132" s="3"/>
-      <c r="G132" s="3"/>
-      <c r="H132" s="3"/>
-      <c r="I132" s="3"/>
+      <c r="F132" s="3">
+        <v>11</v>
+      </c>
+      <c r="G132" s="3">
+        <v>7</v>
+      </c>
+      <c r="H132" s="3">
+        <v>11</v>
+      </c>
+      <c r="I132" s="3">
+        <v>5</v>
+      </c>
       <c r="J132" s="3"/>
       <c r="K132" s="3"/>
       <c r="L132" s="3"/>
       <c r="M132" s="3"/>
       <c r="N132" s="3"/>
-      <c r="O132" s="25"/>
+      <c r="O132" s="3"/>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="7">
@@ -5986,16 +5954,32 @@
       <c r="E133" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="F133" s="4"/>
-      <c r="G133" s="4"/>
-      <c r="H133" s="4"/>
-      <c r="I133" s="4"/>
-      <c r="J133" s="4"/>
-      <c r="K133" s="4"/>
-      <c r="L133" s="4"/>
-      <c r="M133" s="4"/>
+      <c r="F133" s="4">
+        <v>11</v>
+      </c>
+      <c r="G133" s="4">
+        <v>6</v>
+      </c>
+      <c r="H133" s="4">
+        <v>7</v>
+      </c>
+      <c r="I133" s="4">
+        <v>11</v>
+      </c>
+      <c r="J133" s="4">
+        <v>9</v>
+      </c>
+      <c r="K133" s="4">
+        <v>11</v>
+      </c>
+      <c r="L133" s="4">
+        <v>9</v>
+      </c>
+      <c r="M133" s="4">
+        <v>11</v>
+      </c>
       <c r="N133" s="4"/>
-      <c r="O133" s="26"/>
+      <c r="O133" s="4"/>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="7">
@@ -6034,7 +6018,7 @@
       <c r="L134" s="3"/>
       <c r="M134" s="3"/>
       <c r="N134" s="3"/>
-      <c r="O134" s="25"/>
+      <c r="O134" s="3"/>
     </row>
     <row r="135" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A135" s="9">
@@ -6052,16 +6036,16 @@
       <c r="E135" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F135" s="2"/>
-      <c r="G135" s="2"/>
-      <c r="H135" s="2"/>
-      <c r="I135" s="2"/>
-      <c r="J135" s="2"/>
-      <c r="K135" s="2"/>
-      <c r="L135" s="2"/>
-      <c r="M135" s="2"/>
-      <c r="N135" s="2"/>
-      <c r="O135" s="27"/>
+      <c r="F135" s="23"/>
+      <c r="G135" s="23"/>
+      <c r="H135" s="23"/>
+      <c r="I135" s="23"/>
+      <c r="J135" s="23"/>
+      <c r="K135" s="23"/>
+      <c r="L135" s="23"/>
+      <c r="M135" s="23"/>
+      <c r="N135" s="23"/>
+      <c r="O135" s="23"/>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A136" s="5">
@@ -6088,7 +6072,7 @@
       <c r="L136" s="1"/>
       <c r="M136" s="1"/>
       <c r="N136" s="1"/>
-      <c r="O136" s="24"/>
+      <c r="O136" s="1"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="7">
@@ -6131,7 +6115,7 @@
         <v>11</v>
       </c>
       <c r="N137" s="3"/>
-      <c r="O137" s="25"/>
+      <c r="O137" s="3"/>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="7">
@@ -6158,7 +6142,7 @@
       <c r="L138" s="4"/>
       <c r="M138" s="4"/>
       <c r="N138" s="4"/>
-      <c r="O138" s="26"/>
+      <c r="O138" s="4"/>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="7">
@@ -6185,7 +6169,7 @@
       <c r="L139" s="3"/>
       <c r="M139" s="3"/>
       <c r="N139" s="3"/>
-      <c r="O139" s="25"/>
+      <c r="O139" s="3"/>
     </row>
     <row r="140" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A140" s="9">
@@ -6212,7 +6196,7 @@
       <c r="L140" s="2"/>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
-      <c r="O140" s="27"/>
+      <c r="O140" s="2"/>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="5">
@@ -6239,7 +6223,7 @@
       <c r="L141" s="17"/>
       <c r="M141" s="17"/>
       <c r="N141" s="17"/>
-      <c r="O141" s="29"/>
+      <c r="O141" s="17"/>
     </row>
     <row r="142" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A142" s="7">
@@ -6266,7 +6250,7 @@
       <c r="L142" s="3"/>
       <c r="M142" s="3"/>
       <c r="N142" s="3"/>
-      <c r="O142" s="25"/>
+      <c r="O142" s="3"/>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="7">
@@ -6293,7 +6277,7 @@
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
       <c r="N143" s="4"/>
-      <c r="O143" s="26"/>
+      <c r="O143" s="4"/>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="7">
@@ -6320,7 +6304,7 @@
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
       <c r="N144" s="3"/>
-      <c r="O144" s="25"/>
+      <c r="O144" s="3"/>
     </row>
     <row r="145" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A145" s="9">
@@ -6347,7 +6331,7 @@
       <c r="L145" s="2"/>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
-      <c r="O145" s="27"/>
+      <c r="O145" s="2"/>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="5">
@@ -6374,7 +6358,7 @@
       <c r="L146" s="1"/>
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>
-      <c r="O146" s="24"/>
+      <c r="O146" s="1"/>
     </row>
     <row r="147" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A147" s="7">
@@ -6401,7 +6385,7 @@
       <c r="L147" s="3"/>
       <c r="M147" s="3"/>
       <c r="N147" s="3"/>
-      <c r="O147" s="25"/>
+      <c r="O147" s="3"/>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="7">
@@ -6428,7 +6412,7 @@
       <c r="L148" s="4"/>
       <c r="M148" s="4"/>
       <c r="N148" s="4"/>
-      <c r="O148" s="26"/>
+      <c r="O148" s="4"/>
     </row>
     <row r="149" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A149" s="7">
@@ -6455,7 +6439,7 @@
       <c r="L149" s="3"/>
       <c r="M149" s="3"/>
       <c r="N149" s="3"/>
-      <c r="O149" s="25"/>
+      <c r="O149" s="3"/>
     </row>
     <row r="150" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A150" s="5">
@@ -6482,7 +6466,7 @@
       <c r="L150" s="1"/>
       <c r="M150" s="1"/>
       <c r="N150" s="1"/>
-      <c r="O150" s="24"/>
+      <c r="O150" s="1"/>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="7">
@@ -6509,7 +6493,7 @@
       <c r="L151" s="3"/>
       <c r="M151" s="3"/>
       <c r="N151" s="3"/>
-      <c r="O151" s="25"/>
+      <c r="O151" s="3"/>
     </row>
     <row r="152" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A152" s="7">
@@ -6536,7 +6520,7 @@
       <c r="L152" s="4"/>
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
-      <c r="O152" s="26"/>
+      <c r="O152" s="4"/>
     </row>
     <row r="153" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A153" s="7">
@@ -6563,7 +6547,7 @@
       <c r="L153" s="3"/>
       <c r="M153" s="3"/>
       <c r="N153" s="3"/>
-      <c r="O153" s="25"/>
+      <c r="O153" s="3"/>
     </row>
     <row r="154" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A154" s="9">
@@ -6590,7 +6574,7 @@
       <c r="L154" s="2"/>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
-      <c r="O154" s="27"/>
+      <c r="O154" s="2"/>
     </row>
     <row r="155" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A155" s="7">
@@ -6617,7 +6601,7 @@
       <c r="L155" s="3"/>
       <c r="M155" s="3"/>
       <c r="N155" s="3"/>
-      <c r="O155" s="25"/>
+      <c r="O155" s="3"/>
     </row>
     <row r="156" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A156" s="7">
@@ -6644,7 +6628,7 @@
       <c r="L156" s="4"/>
       <c r="M156" s="4"/>
       <c r="N156" s="4"/>
-      <c r="O156" s="26"/>
+      <c r="O156" s="4"/>
     </row>
     <row r="157" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A157" s="9">
@@ -6671,7 +6655,7 @@
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
-      <c r="O157" s="27"/>
+      <c r="O157" s="2"/>
     </row>
     <row r="158" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A158" s="7">
@@ -6698,7 +6682,7 @@
       <c r="L158" s="3"/>
       <c r="M158" s="3"/>
       <c r="N158" s="3"/>
-      <c r="O158" s="25"/>
+      <c r="O158" s="3"/>
     </row>
     <row r="159" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A159" s="7">
@@ -6725,7 +6709,7 @@
       <c r="L159" s="4"/>
       <c r="M159" s="4"/>
       <c r="N159" s="4"/>
-      <c r="O159" s="26"/>
+      <c r="O159" s="4"/>
     </row>
     <row r="160" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A160" s="7">
@@ -6752,7 +6736,7 @@
       <c r="L160" s="3"/>
       <c r="M160" s="3"/>
       <c r="N160" s="3"/>
-      <c r="O160" s="25"/>
+      <c r="O160" s="3"/>
     </row>
     <row r="161" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A161" s="9">
@@ -6779,7 +6763,7 @@
       <c r="L161" s="16"/>
       <c r="M161" s="16"/>
       <c r="N161" s="16"/>
-      <c r="O161" s="28"/>
+      <c r="O161" s="16"/>
     </row>
     <row r="162" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A162" s="5">
@@ -6806,7 +6790,7 @@
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
       <c r="N162" s="1"/>
-      <c r="O162" s="24"/>
+      <c r="O162" s="1"/>
     </row>
     <row r="163" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A163" s="7">
@@ -6833,7 +6817,7 @@
       <c r="L163" s="3"/>
       <c r="M163" s="3"/>
       <c r="N163" s="3"/>
-      <c r="O163" s="25"/>
+      <c r="O163" s="3"/>
     </row>
     <row r="164" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A164" s="7">
@@ -6860,7 +6844,7 @@
       <c r="L164" s="4"/>
       <c r="M164" s="4"/>
       <c r="N164" s="4"/>
-      <c r="O164" s="26"/>
+      <c r="O164" s="4"/>
     </row>
     <row r="165" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A165" s="7">
@@ -6887,7 +6871,7 @@
       <c r="L165" s="3"/>
       <c r="M165" s="3"/>
       <c r="N165" s="3"/>
-      <c r="O165" s="25"/>
+      <c r="O165" s="3"/>
     </row>
     <row r="166" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A166" s="9">
@@ -6914,7 +6898,7 @@
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
-      <c r="O166" s="27"/>
+      <c r="O166" s="2"/>
     </row>
     <row r="167" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A167" s="5">
@@ -6941,7 +6925,7 @@
       <c r="L167" s="1"/>
       <c r="M167" s="1"/>
       <c r="N167" s="1"/>
-      <c r="O167" s="24"/>
+      <c r="O167" s="1"/>
     </row>
     <row r="168" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A168" s="7">
@@ -6968,7 +6952,7 @@
       <c r="L168" s="4"/>
       <c r="M168" s="4"/>
       <c r="N168" s="4"/>
-      <c r="O168" s="26"/>
+      <c r="O168" s="4"/>
     </row>
     <row r="169" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A169" s="7">
@@ -6995,7 +6979,7 @@
       <c r="L169" s="3"/>
       <c r="M169" s="3"/>
       <c r="N169" s="3"/>
-      <c r="O169" s="25"/>
+      <c r="O169" s="3"/>
     </row>
     <row r="170" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A170" s="9">
@@ -7022,7 +7006,7 @@
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
-      <c r="O170" s="27"/>
+      <c r="O170" s="2"/>
     </row>
     <row r="171" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A171" s="5">
@@ -7049,7 +7033,7 @@
       <c r="L171" s="1"/>
       <c r="M171" s="1"/>
       <c r="N171" s="1"/>
-      <c r="O171" s="24"/>
+      <c r="O171" s="1"/>
     </row>
     <row r="172" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A172" s="7">
@@ -7076,7 +7060,7 @@
       <c r="L172" s="3"/>
       <c r="M172" s="3"/>
       <c r="N172" s="3"/>
-      <c r="O172" s="25"/>
+      <c r="O172" s="3"/>
     </row>
     <row r="173" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A173" s="7">
@@ -7103,7 +7087,7 @@
       <c r="L173" s="4"/>
       <c r="M173" s="4"/>
       <c r="N173" s="4"/>
-      <c r="O173" s="26"/>
+      <c r="O173" s="4"/>
     </row>
     <row r="174" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A174" s="9">
@@ -7121,16 +7105,16 @@
       <c r="E174" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-      <c r="H174" s="2"/>
-      <c r="I174" s="2"/>
-      <c r="J174" s="2"/>
-      <c r="K174" s="2"/>
-      <c r="L174" s="2"/>
-      <c r="M174" s="2"/>
-      <c r="N174" s="2"/>
-      <c r="O174" s="27"/>
+      <c r="F174" s="3"/>
+      <c r="G174" s="3"/>
+      <c r="H174" s="3"/>
+      <c r="I174" s="3"/>
+      <c r="J174" s="3"/>
+      <c r="K174" s="3"/>
+      <c r="L174" s="3"/>
+      <c r="M174" s="3"/>
+      <c r="N174" s="3"/>
+      <c r="O174" s="3"/>
     </row>
     <row r="175" spans="1:15" x14ac:dyDescent="0.3">
       <c r="B175" s="12"/>

--- a/RESULTADOS T6.xlsx
+++ b/RESULTADOS T6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{954073BE-7BC1-49E2-8617-44D2CB007BCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BB1CE9E-3B3B-40A6-AC09-1A1E64887838}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -336,7 +336,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -401,6 +401,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6063,12 +6066,24 @@
       <c r="E136" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F136" s="1"/>
-      <c r="G136" s="1"/>
-      <c r="H136" s="1"/>
-      <c r="I136" s="1"/>
-      <c r="J136" s="1"/>
-      <c r="K136" s="1"/>
+      <c r="F136" s="1">
+        <v>7</v>
+      </c>
+      <c r="G136" s="1">
+        <v>11</v>
+      </c>
+      <c r="H136" s="1">
+        <v>7</v>
+      </c>
+      <c r="I136" s="1">
+        <v>11</v>
+      </c>
+      <c r="J136" s="1">
+        <v>6</v>
+      </c>
+      <c r="K136" s="1">
+        <v>11</v>
+      </c>
       <c r="L136" s="1"/>
       <c r="M136" s="1"/>
       <c r="N136" s="1"/>
@@ -6133,14 +6148,30 @@
       <c r="E138" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F138" s="4"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="4"/>
-      <c r="K138" s="4"/>
-      <c r="L138" s="4"/>
-      <c r="M138" s="4"/>
+      <c r="F138" s="4">
+        <v>6</v>
+      </c>
+      <c r="G138" s="4">
+        <v>11</v>
+      </c>
+      <c r="H138" s="4">
+        <v>11</v>
+      </c>
+      <c r="I138" s="4">
+        <v>8</v>
+      </c>
+      <c r="J138" s="4">
+        <v>11</v>
+      </c>
+      <c r="K138" s="4">
+        <v>6</v>
+      </c>
+      <c r="L138" s="4">
+        <v>11</v>
+      </c>
+      <c r="M138" s="4">
+        <v>5</v>
+      </c>
       <c r="N138" s="4"/>
       <c r="O138" s="4"/>
     </row>
@@ -6160,10 +6191,18 @@
       <c r="E139" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F139" s="3"/>
-      <c r="G139" s="3"/>
-      <c r="H139" s="3"/>
-      <c r="I139" s="3"/>
+      <c r="F139" s="3">
+        <v>11</v>
+      </c>
+      <c r="G139" s="3">
+        <v>4</v>
+      </c>
+      <c r="H139" s="3">
+        <v>11</v>
+      </c>
+      <c r="I139" s="3">
+        <v>6</v>
+      </c>
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="3"/>
@@ -6187,14 +6226,30 @@
       <c r="E140" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-      <c r="H140" s="2"/>
-      <c r="I140" s="2"/>
-      <c r="J140" s="2"/>
-      <c r="K140" s="2"/>
-      <c r="L140" s="2"/>
-      <c r="M140" s="2"/>
+      <c r="F140" s="2">
+        <v>13</v>
+      </c>
+      <c r="G140" s="2">
+        <v>11</v>
+      </c>
+      <c r="H140" s="2">
+        <v>4</v>
+      </c>
+      <c r="I140" s="2">
+        <v>11</v>
+      </c>
+      <c r="J140" s="2">
+        <v>9</v>
+      </c>
+      <c r="K140" s="2">
+        <v>11</v>
+      </c>
+      <c r="L140" s="2">
+        <v>3</v>
+      </c>
+      <c r="M140" s="2">
+        <v>11</v>
+      </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
     </row>
@@ -6241,16 +6296,36 @@
       <c r="E142" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F142" s="3"/>
-      <c r="G142" s="3"/>
-      <c r="H142" s="3"/>
-      <c r="I142" s="3"/>
-      <c r="J142" s="3"/>
-      <c r="K142" s="3"/>
-      <c r="L142" s="3"/>
-      <c r="M142" s="3"/>
-      <c r="N142" s="3"/>
-      <c r="O142" s="3"/>
+      <c r="F142" s="3">
+        <v>11</v>
+      </c>
+      <c r="G142" s="3">
+        <v>9</v>
+      </c>
+      <c r="H142" s="3">
+        <v>8</v>
+      </c>
+      <c r="I142" s="3">
+        <v>11</v>
+      </c>
+      <c r="J142" s="3">
+        <v>11</v>
+      </c>
+      <c r="K142" s="3">
+        <v>9</v>
+      </c>
+      <c r="L142" s="3">
+        <v>8</v>
+      </c>
+      <c r="M142" s="3">
+        <v>11</v>
+      </c>
+      <c r="N142" s="3">
+        <v>4</v>
+      </c>
+      <c r="O142" s="3">
+        <v>11</v>
+      </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="7">
@@ -6268,16 +6343,16 @@
       <c r="E143" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="F143" s="4"/>
-      <c r="G143" s="4"/>
-      <c r="H143" s="4"/>
-      <c r="I143" s="4"/>
-      <c r="J143" s="4"/>
-      <c r="K143" s="4"/>
-      <c r="L143" s="4"/>
-      <c r="M143" s="4"/>
-      <c r="N143" s="4"/>
-      <c r="O143" s="4"/>
+      <c r="F143" s="24"/>
+      <c r="G143" s="24"/>
+      <c r="H143" s="24"/>
+      <c r="I143" s="24"/>
+      <c r="J143" s="24"/>
+      <c r="K143" s="24"/>
+      <c r="L143" s="24"/>
+      <c r="M143" s="24"/>
+      <c r="N143" s="24"/>
+      <c r="O143" s="24"/>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="7">
@@ -6295,12 +6370,24 @@
       <c r="E144" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F144" s="3"/>
-      <c r="G144" s="3"/>
-      <c r="H144" s="3"/>
-      <c r="I144" s="3"/>
-      <c r="J144" s="3"/>
-      <c r="K144" s="3"/>
+      <c r="F144" s="3">
+        <v>8</v>
+      </c>
+      <c r="G144" s="3">
+        <v>11</v>
+      </c>
+      <c r="H144" s="3">
+        <v>12</v>
+      </c>
+      <c r="I144" s="3">
+        <v>10</v>
+      </c>
+      <c r="J144" s="3">
+        <v>4</v>
+      </c>
+      <c r="K144" s="3">
+        <v>11</v>
+      </c>
       <c r="L144" s="3"/>
       <c r="M144" s="3"/>
       <c r="N144" s="3"/>
@@ -6322,16 +6409,36 @@
       <c r="E145" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="F145" s="2"/>
-      <c r="G145" s="2"/>
-      <c r="H145" s="2"/>
-      <c r="I145" s="2"/>
-      <c r="J145" s="2"/>
-      <c r="K145" s="2"/>
-      <c r="L145" s="2"/>
-      <c r="M145" s="2"/>
-      <c r="N145" s="2"/>
-      <c r="O145" s="2"/>
+      <c r="F145" s="2">
+        <v>11</v>
+      </c>
+      <c r="G145" s="2">
+        <v>4</v>
+      </c>
+      <c r="H145" s="2">
+        <v>3</v>
+      </c>
+      <c r="I145" s="2">
+        <v>11</v>
+      </c>
+      <c r="J145" s="2">
+        <v>11</v>
+      </c>
+      <c r="K145" s="2">
+        <v>9</v>
+      </c>
+      <c r="L145" s="2">
+        <v>5</v>
+      </c>
+      <c r="M145" s="2">
+        <v>11</v>
+      </c>
+      <c r="N145" s="2">
+        <v>9</v>
+      </c>
+      <c r="O145" s="2">
+        <v>11</v>
+      </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="5">

--- a/RESULTADOS T6.xlsx
+++ b/RESULTADOS T6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A19577-A532-4930-BEE8-5855B833A98B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29441448-7F5E-4478-9666-34436A9DC26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -378,7 +378,7 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -4856,16 +4856,36 @@
       <c r="E105" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F105" s="19"/>
-      <c r="G105" s="19"/>
-      <c r="H105" s="19"/>
-      <c r="I105" s="19"/>
-      <c r="J105" s="19"/>
-      <c r="K105" s="19"/>
-      <c r="L105" s="19"/>
-      <c r="M105" s="19"/>
-      <c r="N105" s="19"/>
-      <c r="O105" s="19"/>
+      <c r="F105" s="3">
+        <v>8</v>
+      </c>
+      <c r="G105" s="3">
+        <v>11</v>
+      </c>
+      <c r="H105" s="3">
+        <v>11</v>
+      </c>
+      <c r="I105" s="3">
+        <v>5</v>
+      </c>
+      <c r="J105" s="3">
+        <v>11</v>
+      </c>
+      <c r="K105" s="3">
+        <v>6</v>
+      </c>
+      <c r="L105" s="3">
+        <v>11</v>
+      </c>
+      <c r="M105" s="3">
+        <v>13</v>
+      </c>
+      <c r="N105" s="3">
+        <v>11</v>
+      </c>
+      <c r="O105" s="3">
+        <v>4</v>
+      </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A106" s="7">
@@ -5808,16 +5828,24 @@
       <c r="E129" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F129" s="20"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="20"/>
-      <c r="I129" s="20"/>
-      <c r="J129" s="20"/>
-      <c r="K129" s="20"/>
-      <c r="L129" s="20"/>
-      <c r="M129" s="20"/>
-      <c r="N129" s="20"/>
-      <c r="O129" s="20"/>
+      <c r="F129" s="4">
+        <v>8</v>
+      </c>
+      <c r="G129" s="4">
+        <v>11</v>
+      </c>
+      <c r="H129" s="4">
+        <v>2</v>
+      </c>
+      <c r="I129" s="4">
+        <v>11</v>
+      </c>
+      <c r="J129" s="4"/>
+      <c r="K129" s="4"/>
+      <c r="L129" s="4"/>
+      <c r="M129" s="4"/>
+      <c r="N129" s="4"/>
+      <c r="O129" s="4"/>
     </row>
     <row r="130" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A130" s="7">
@@ -5921,16 +5949,16 @@
       <c r="E132" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F132" s="1"/>
-      <c r="G132" s="1"/>
-      <c r="H132" s="1"/>
-      <c r="I132" s="1"/>
-      <c r="J132" s="1"/>
-      <c r="K132" s="1"/>
-      <c r="L132" s="1"/>
-      <c r="M132" s="1"/>
-      <c r="N132" s="1"/>
-      <c r="O132" s="1"/>
+      <c r="F132" s="20"/>
+      <c r="G132" s="20"/>
+      <c r="H132" s="20"/>
+      <c r="I132" s="20"/>
+      <c r="J132" s="20"/>
+      <c r="K132" s="20"/>
+      <c r="L132" s="20"/>
+      <c r="M132" s="20"/>
+      <c r="N132" s="20"/>
+      <c r="O132" s="20"/>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="7">
@@ -5948,16 +5976,16 @@
       <c r="E133" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F133" s="3"/>
-      <c r="G133" s="3"/>
-      <c r="H133" s="3"/>
-      <c r="I133" s="3"/>
-      <c r="J133" s="3"/>
-      <c r="K133" s="3"/>
-      <c r="L133" s="3"/>
-      <c r="M133" s="3"/>
-      <c r="N133" s="3"/>
-      <c r="O133" s="3"/>
+      <c r="F133" s="19"/>
+      <c r="G133" s="19"/>
+      <c r="H133" s="19"/>
+      <c r="I133" s="19"/>
+      <c r="J133" s="19"/>
+      <c r="K133" s="19"/>
+      <c r="L133" s="19"/>
+      <c r="M133" s="19"/>
+      <c r="N133" s="19"/>
+      <c r="O133" s="19"/>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="7">
@@ -5975,10 +6003,18 @@
       <c r="E134" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="F134" s="4"/>
-      <c r="G134" s="4"/>
-      <c r="H134" s="4"/>
-      <c r="I134" s="4"/>
+      <c r="F134" s="4">
+        <v>5</v>
+      </c>
+      <c r="G134" s="4">
+        <v>11</v>
+      </c>
+      <c r="H134" s="4">
+        <v>10</v>
+      </c>
+      <c r="I134" s="4">
+        <v>12</v>
+      </c>
       <c r="J134" s="4"/>
       <c r="K134" s="4"/>
       <c r="L134" s="4"/>
@@ -6002,10 +6038,18 @@
       <c r="E135" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F135" s="3"/>
-      <c r="G135" s="3"/>
-      <c r="H135" s="3"/>
-      <c r="I135" s="3"/>
+      <c r="F135" s="3">
+        <v>5</v>
+      </c>
+      <c r="G135" s="3">
+        <v>11</v>
+      </c>
+      <c r="H135" s="3">
+        <v>7</v>
+      </c>
+      <c r="I135" s="3">
+        <v>11</v>
+      </c>
       <c r="J135" s="3"/>
       <c r="K135" s="3"/>
       <c r="L135" s="3"/>

--- a/RESULTADOS T6.xlsx
+++ b/RESULTADOS T6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29441448-7F5E-4478-9666-34436A9DC26D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D749542-0037-4718-A338-104D9D37EAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -323,7 +323,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -379,6 +379,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6073,16 +6076,16 @@
       <c r="E136" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F136" s="1"/>
-      <c r="G136" s="1"/>
-      <c r="H136" s="1"/>
-      <c r="I136" s="1"/>
-      <c r="J136" s="1"/>
-      <c r="K136" s="1"/>
-      <c r="L136" s="1"/>
-      <c r="M136" s="1"/>
-      <c r="N136" s="1"/>
-      <c r="O136" s="1"/>
+      <c r="F136" s="20"/>
+      <c r="G136" s="20"/>
+      <c r="H136" s="20"/>
+      <c r="I136" s="20"/>
+      <c r="J136" s="20"/>
+      <c r="K136" s="20"/>
+      <c r="L136" s="20"/>
+      <c r="M136" s="20"/>
+      <c r="N136" s="20"/>
+      <c r="O136" s="20"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="7">
@@ -6100,16 +6103,16 @@
       <c r="E137" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F137" s="3"/>
-      <c r="G137" s="3"/>
-      <c r="H137" s="3"/>
-      <c r="I137" s="3"/>
-      <c r="J137" s="3"/>
-      <c r="K137" s="3"/>
-      <c r="L137" s="3"/>
-      <c r="M137" s="3"/>
-      <c r="N137" s="3"/>
-      <c r="O137" s="3"/>
+      <c r="F137" s="19"/>
+      <c r="G137" s="19"/>
+      <c r="H137" s="19"/>
+      <c r="I137" s="19"/>
+      <c r="J137" s="19"/>
+      <c r="K137" s="19"/>
+      <c r="L137" s="19"/>
+      <c r="M137" s="19"/>
+      <c r="N137" s="19"/>
+      <c r="O137" s="19"/>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="7">
@@ -6127,16 +6130,16 @@
       <c r="E138" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F138" s="4"/>
-      <c r="G138" s="4"/>
-      <c r="H138" s="4"/>
-      <c r="I138" s="4"/>
-      <c r="J138" s="4"/>
-      <c r="K138" s="4"/>
-      <c r="L138" s="4"/>
-      <c r="M138" s="4"/>
-      <c r="N138" s="4"/>
-      <c r="O138" s="4"/>
+      <c r="F138" s="21"/>
+      <c r="G138" s="21"/>
+      <c r="H138" s="21"/>
+      <c r="I138" s="21"/>
+      <c r="J138" s="21"/>
+      <c r="K138" s="21"/>
+      <c r="L138" s="21"/>
+      <c r="M138" s="21"/>
+      <c r="N138" s="21"/>
+      <c r="O138" s="21"/>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="7">
@@ -6154,10 +6157,18 @@
       <c r="E139" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="F139" s="3"/>
-      <c r="G139" s="3"/>
-      <c r="H139" s="3"/>
-      <c r="I139" s="3"/>
+      <c r="F139" s="3">
+        <v>3</v>
+      </c>
+      <c r="G139" s="3">
+        <v>11</v>
+      </c>
+      <c r="H139" s="3">
+        <v>7</v>
+      </c>
+      <c r="I139" s="3">
+        <v>11</v>
+      </c>
       <c r="J139" s="3"/>
       <c r="K139" s="3"/>
       <c r="L139" s="3"/>
@@ -6181,16 +6192,36 @@
       <c r="E140" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="F140" s="2"/>
-      <c r="G140" s="2"/>
-      <c r="H140" s="2"/>
-      <c r="I140" s="2"/>
-      <c r="J140" s="2"/>
-      <c r="K140" s="2"/>
-      <c r="L140" s="2"/>
-      <c r="M140" s="2"/>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
+      <c r="F140" s="2">
+        <v>9</v>
+      </c>
+      <c r="G140" s="2">
+        <v>11</v>
+      </c>
+      <c r="H140" s="2">
+        <v>11</v>
+      </c>
+      <c r="I140" s="2">
+        <v>9</v>
+      </c>
+      <c r="J140" s="2">
+        <v>11</v>
+      </c>
+      <c r="K140" s="2">
+        <v>5</v>
+      </c>
+      <c r="L140" s="2">
+        <v>5</v>
+      </c>
+      <c r="M140" s="2">
+        <v>11</v>
+      </c>
+      <c r="N140" s="2">
+        <v>10</v>
+      </c>
+      <c r="O140" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="141" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A141" s="7">

--- a/RESULTADOS T6.xlsx
+++ b/RESULTADOS T6.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D749542-0037-4718-A338-104D9D37EAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5511A4-1FF0-4999-82A2-6371EDF121E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -323,7 +323,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -379,9 +379,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6130,16 +6127,24 @@
       <c r="E138" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="F138" s="21"/>
-      <c r="G138" s="21"/>
-      <c r="H138" s="21"/>
-      <c r="I138" s="21"/>
-      <c r="J138" s="21"/>
-      <c r="K138" s="21"/>
-      <c r="L138" s="21"/>
-      <c r="M138" s="21"/>
-      <c r="N138" s="21"/>
-      <c r="O138" s="21"/>
+      <c r="F138" s="4">
+        <v>7</v>
+      </c>
+      <c r="G138" s="4">
+        <v>11</v>
+      </c>
+      <c r="H138" s="4">
+        <v>3</v>
+      </c>
+      <c r="I138" s="4">
+        <v>11</v>
+      </c>
+      <c r="J138" s="4"/>
+      <c r="K138" s="4"/>
+      <c r="L138" s="4"/>
+      <c r="M138" s="4"/>
+      <c r="N138" s="4"/>
+      <c r="O138" s="4"/>
     </row>
     <row r="139" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A139" s="7">
@@ -6239,10 +6244,18 @@
       <c r="E141" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="F141" s="4"/>
-      <c r="G141" s="4"/>
-      <c r="H141" s="4"/>
-      <c r="I141" s="4"/>
+      <c r="F141" s="4">
+        <v>4</v>
+      </c>
+      <c r="G141" s="4">
+        <v>11</v>
+      </c>
+      <c r="H141" s="4">
+        <v>9</v>
+      </c>
+      <c r="I141" s="4">
+        <v>11</v>
+      </c>
       <c r="J141" s="4"/>
       <c r="K141" s="4"/>
       <c r="L141" s="4"/>
@@ -6266,16 +6279,36 @@
       <c r="E142" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-      <c r="H142" s="2"/>
-      <c r="I142" s="2"/>
-      <c r="J142" s="2"/>
-      <c r="K142" s="2"/>
-      <c r="L142" s="2"/>
-      <c r="M142" s="2"/>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
+      <c r="F142" s="2">
+        <v>11</v>
+      </c>
+      <c r="G142" s="2">
+        <v>5</v>
+      </c>
+      <c r="H142" s="2">
+        <v>11</v>
+      </c>
+      <c r="I142" s="2">
+        <v>13</v>
+      </c>
+      <c r="J142" s="2">
+        <v>11</v>
+      </c>
+      <c r="K142" s="2">
+        <v>3</v>
+      </c>
+      <c r="L142" s="2">
+        <v>10</v>
+      </c>
+      <c r="M142" s="2">
+        <v>12</v>
+      </c>
+      <c r="N142" s="2">
+        <v>11</v>
+      </c>
+      <c r="O142" s="2">
+        <v>6</v>
+      </c>
     </row>
     <row r="143" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A143" s="7">
@@ -6374,12 +6407,24 @@
       <c r="E146" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F146" s="1"/>
-      <c r="G146" s="1"/>
-      <c r="H146" s="1"/>
-      <c r="I146" s="1"/>
-      <c r="J146" s="1"/>
-      <c r="K146" s="1"/>
+      <c r="F146" s="1">
+        <v>11</v>
+      </c>
+      <c r="G146" s="1">
+        <v>3</v>
+      </c>
+      <c r="H146" s="1">
+        <v>11</v>
+      </c>
+      <c r="I146" s="1">
+        <v>8</v>
+      </c>
+      <c r="J146" s="1">
+        <v>15</v>
+      </c>
+      <c r="K146" s="1">
+        <v>13</v>
+      </c>
       <c r="L146" s="1"/>
       <c r="M146" s="1"/>
       <c r="N146" s="1"/>

--- a/RESULTADOS T6.xlsx
+++ b/RESULTADOS T6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5511A4-1FF0-4999-82A2-6371EDF121E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96178018-75F8-4C64-B0A7-0BC402C09941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -376,9 +376,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5949,16 +5946,32 @@
       <c r="E132" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F132" s="20"/>
-      <c r="G132" s="20"/>
-      <c r="H132" s="20"/>
-      <c r="I132" s="20"/>
-      <c r="J132" s="20"/>
-      <c r="K132" s="20"/>
-      <c r="L132" s="20"/>
-      <c r="M132" s="20"/>
-      <c r="N132" s="20"/>
-      <c r="O132" s="20"/>
+      <c r="F132" s="1">
+        <v>2</v>
+      </c>
+      <c r="G132" s="1">
+        <v>11</v>
+      </c>
+      <c r="H132" s="1">
+        <v>7</v>
+      </c>
+      <c r="I132" s="1">
+        <v>11</v>
+      </c>
+      <c r="J132" s="1">
+        <v>14</v>
+      </c>
+      <c r="K132" s="1">
+        <v>12</v>
+      </c>
+      <c r="L132" s="1">
+        <v>9</v>
+      </c>
+      <c r="M132" s="1">
+        <v>11</v>
+      </c>
+      <c r="N132" s="1"/>
+      <c r="O132" s="1"/>
     </row>
     <row r="133" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A133" s="7">
@@ -6073,16 +6086,28 @@
       <c r="E136" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F136" s="20"/>
-      <c r="G136" s="20"/>
-      <c r="H136" s="20"/>
-      <c r="I136" s="20"/>
-      <c r="J136" s="20"/>
-      <c r="K136" s="20"/>
-      <c r="L136" s="20"/>
-      <c r="M136" s="20"/>
-      <c r="N136" s="20"/>
-      <c r="O136" s="20"/>
+      <c r="F136" s="1">
+        <v>11</v>
+      </c>
+      <c r="G136" s="1">
+        <v>13</v>
+      </c>
+      <c r="H136" s="1">
+        <v>4</v>
+      </c>
+      <c r="I136" s="1">
+        <v>11</v>
+      </c>
+      <c r="J136" s="1">
+        <v>2</v>
+      </c>
+      <c r="K136" s="1">
+        <v>11</v>
+      </c>
+      <c r="L136" s="1"/>
+      <c r="M136" s="1"/>
+      <c r="N136" s="1"/>
+      <c r="O136" s="1"/>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A137" s="7">
@@ -6100,16 +6125,28 @@
       <c r="E137" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="F137" s="19"/>
-      <c r="G137" s="19"/>
-      <c r="H137" s="19"/>
-      <c r="I137" s="19"/>
-      <c r="J137" s="19"/>
-      <c r="K137" s="19"/>
-      <c r="L137" s="19"/>
-      <c r="M137" s="19"/>
-      <c r="N137" s="19"/>
-      <c r="O137" s="19"/>
+      <c r="F137" s="3">
+        <v>6</v>
+      </c>
+      <c r="G137" s="3">
+        <v>11</v>
+      </c>
+      <c r="H137" s="3">
+        <v>6</v>
+      </c>
+      <c r="I137" s="3">
+        <v>11</v>
+      </c>
+      <c r="J137" s="3">
+        <v>5</v>
+      </c>
+      <c r="K137" s="3">
+        <v>11</v>
+      </c>
+      <c r="L137" s="3"/>
+      <c r="M137" s="3"/>
+      <c r="N137" s="3"/>
+      <c r="O137" s="3"/>
     </row>
     <row r="138" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A138" s="7">
@@ -6326,16 +6363,16 @@
       <c r="E143" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F143" s="3"/>
-      <c r="G143" s="3"/>
-      <c r="H143" s="3"/>
-      <c r="I143" s="3"/>
-      <c r="J143" s="3"/>
-      <c r="K143" s="3"/>
-      <c r="L143" s="3"/>
-      <c r="M143" s="3"/>
-      <c r="N143" s="3"/>
-      <c r="O143" s="3"/>
+      <c r="F143" s="19"/>
+      <c r="G143" s="19"/>
+      <c r="H143" s="19"/>
+      <c r="I143" s="19"/>
+      <c r="J143" s="19"/>
+      <c r="K143" s="19"/>
+      <c r="L143" s="19"/>
+      <c r="M143" s="19"/>
+      <c r="N143" s="19"/>
+      <c r="O143" s="19"/>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="7">
@@ -6353,10 +6390,18 @@
       <c r="E144" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="F144" s="4"/>
-      <c r="G144" s="4"/>
-      <c r="H144" s="4"/>
-      <c r="I144" s="4"/>
+      <c r="F144" s="4">
+        <v>7</v>
+      </c>
+      <c r="G144" s="4">
+        <v>11</v>
+      </c>
+      <c r="H144" s="4">
+        <v>4</v>
+      </c>
+      <c r="I144" s="4">
+        <v>11</v>
+      </c>
       <c r="J144" s="4"/>
       <c r="K144" s="4"/>
       <c r="L144" s="4"/>
@@ -6380,16 +6425,36 @@
       <c r="E145" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F145" s="3"/>
-      <c r="G145" s="3"/>
-      <c r="H145" s="3"/>
-      <c r="I145" s="3"/>
-      <c r="J145" s="3"/>
-      <c r="K145" s="3"/>
-      <c r="L145" s="3"/>
-      <c r="M145" s="3"/>
-      <c r="N145" s="3"/>
-      <c r="O145" s="3"/>
+      <c r="F145" s="3">
+        <v>9</v>
+      </c>
+      <c r="G145" s="3">
+        <v>11</v>
+      </c>
+      <c r="H145" s="3">
+        <v>6</v>
+      </c>
+      <c r="I145" s="3">
+        <v>11</v>
+      </c>
+      <c r="J145" s="3">
+        <v>11</v>
+      </c>
+      <c r="K145" s="3">
+        <v>7</v>
+      </c>
+      <c r="L145" s="3">
+        <v>11</v>
+      </c>
+      <c r="M145" s="3">
+        <v>8</v>
+      </c>
+      <c r="N145" s="3">
+        <v>11</v>
+      </c>
+      <c r="O145" s="3">
+        <v>9</v>
+      </c>
     </row>
     <row r="146" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A146" s="5">

--- a/RESULTADOS T6.xlsx
+++ b/RESULTADOS T6.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96178018-75F8-4C64-B0A7-0BC402C09941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3368B13F-11F5-479E-97B8-4CAA783EFFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -323,7 +323,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -376,6 +376,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5989,16 +5992,28 @@
       <c r="E133" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F133" s="19"/>
-      <c r="G133" s="19"/>
-      <c r="H133" s="19"/>
-      <c r="I133" s="19"/>
-      <c r="J133" s="19"/>
-      <c r="K133" s="19"/>
-      <c r="L133" s="19"/>
-      <c r="M133" s="19"/>
-      <c r="N133" s="19"/>
-      <c r="O133" s="19"/>
+      <c r="F133" s="3">
+        <v>3</v>
+      </c>
+      <c r="G133" s="3">
+        <v>11</v>
+      </c>
+      <c r="H133" s="3">
+        <v>4</v>
+      </c>
+      <c r="I133" s="3">
+        <v>11</v>
+      </c>
+      <c r="J133" s="3">
+        <v>3</v>
+      </c>
+      <c r="K133" s="3">
+        <v>11</v>
+      </c>
+      <c r="L133" s="3"/>
+      <c r="M133" s="3"/>
+      <c r="N133" s="3"/>
+      <c r="O133" s="3"/>
     </row>
     <row r="134" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A134" s="7">
@@ -6511,16 +6526,16 @@
       <c r="E147" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F147" s="3"/>
-      <c r="G147" s="3"/>
-      <c r="H147" s="3"/>
-      <c r="I147" s="3"/>
-      <c r="J147" s="3"/>
-      <c r="K147" s="3"/>
-      <c r="L147" s="3"/>
-      <c r="M147" s="3"/>
-      <c r="N147" s="3"/>
-      <c r="O147" s="3"/>
+      <c r="F147" s="19"/>
+      <c r="G147" s="19"/>
+      <c r="H147" s="19"/>
+      <c r="I147" s="19"/>
+      <c r="J147" s="19"/>
+      <c r="K147" s="19"/>
+      <c r="L147" s="19"/>
+      <c r="M147" s="19"/>
+      <c r="N147" s="19"/>
+      <c r="O147" s="19"/>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="7">
@@ -6538,14 +6553,30 @@
       <c r="E148" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F148" s="4"/>
-      <c r="G148" s="4"/>
-      <c r="H148" s="4"/>
-      <c r="I148" s="4"/>
-      <c r="J148" s="4"/>
-      <c r="K148" s="4"/>
-      <c r="L148" s="4"/>
-      <c r="M148" s="4"/>
+      <c r="F148" s="4">
+        <v>6</v>
+      </c>
+      <c r="G148" s="4">
+        <v>11</v>
+      </c>
+      <c r="H148" s="4">
+        <v>2</v>
+      </c>
+      <c r="I148" s="4">
+        <v>11</v>
+      </c>
+      <c r="J148" s="4">
+        <v>11</v>
+      </c>
+      <c r="K148" s="4">
+        <v>8</v>
+      </c>
+      <c r="L148" s="4">
+        <v>5</v>
+      </c>
+      <c r="M148" s="4">
+        <v>11</v>
+      </c>
       <c r="N148" s="4"/>
       <c r="O148" s="4"/>
     </row>
@@ -6565,16 +6596,16 @@
       <c r="E149" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F149" s="3"/>
-      <c r="G149" s="3"/>
-      <c r="H149" s="3"/>
-      <c r="I149" s="3"/>
-      <c r="J149" s="3"/>
-      <c r="K149" s="3"/>
-      <c r="L149" s="3"/>
-      <c r="M149" s="3"/>
-      <c r="N149" s="3"/>
-      <c r="O149" s="3"/>
+      <c r="F149" s="19"/>
+      <c r="G149" s="19"/>
+      <c r="H149" s="19"/>
+      <c r="I149" s="19"/>
+      <c r="J149" s="19"/>
+      <c r="K149" s="19"/>
+      <c r="L149" s="19"/>
+      <c r="M149" s="19"/>
+      <c r="N149" s="19"/>
+      <c r="O149" s="19"/>
     </row>
     <row r="150" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="9">
@@ -6592,16 +6623,16 @@
       <c r="E150" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F150" s="2"/>
-      <c r="G150" s="2"/>
-      <c r="H150" s="2"/>
-      <c r="I150" s="2"/>
-      <c r="J150" s="2"/>
-      <c r="K150" s="2"/>
-      <c r="L150" s="2"/>
-      <c r="M150" s="2"/>
-      <c r="N150" s="2"/>
-      <c r="O150" s="2"/>
+      <c r="F150" s="20"/>
+      <c r="G150" s="20"/>
+      <c r="H150" s="20"/>
+      <c r="I150" s="20"/>
+      <c r="J150" s="20"/>
+      <c r="K150" s="20"/>
+      <c r="L150" s="20"/>
+      <c r="M150" s="20"/>
+      <c r="N150" s="20"/>
+      <c r="O150" s="20"/>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="5">

--- a/RESULTADOS T6.xlsx
+++ b/RESULTADOS T6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3368B13F-11F5-479E-97B8-4CAA783EFFFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BA6396-6E0F-4E9F-AD2A-A35379351AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -190,7 +190,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -205,12 +205,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -323,7 +317,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -373,12 +367,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -6378,16 +6366,28 @@
       <c r="E143" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F143" s="19"/>
-      <c r="G143" s="19"/>
-      <c r="H143" s="19"/>
-      <c r="I143" s="19"/>
-      <c r="J143" s="19"/>
-      <c r="K143" s="19"/>
-      <c r="L143" s="19"/>
-      <c r="M143" s="19"/>
-      <c r="N143" s="19"/>
-      <c r="O143" s="19"/>
+      <c r="F143" s="3">
+        <v>11</v>
+      </c>
+      <c r="G143" s="3">
+        <v>5</v>
+      </c>
+      <c r="H143" s="3">
+        <v>11</v>
+      </c>
+      <c r="I143" s="3">
+        <v>7</v>
+      </c>
+      <c r="J143" s="3">
+        <v>11</v>
+      </c>
+      <c r="K143" s="3">
+        <v>3</v>
+      </c>
+      <c r="L143" s="3"/>
+      <c r="M143" s="3"/>
+      <c r="N143" s="3"/>
+      <c r="O143" s="3"/>
     </row>
     <row r="144" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A144" s="7">
@@ -6526,16 +6526,16 @@
       <c r="E147" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F147" s="19"/>
-      <c r="G147" s="19"/>
-      <c r="H147" s="19"/>
-      <c r="I147" s="19"/>
-      <c r="J147" s="19"/>
-      <c r="K147" s="19"/>
-      <c r="L147" s="19"/>
-      <c r="M147" s="19"/>
-      <c r="N147" s="19"/>
-      <c r="O147" s="19"/>
+      <c r="F147" s="3"/>
+      <c r="G147" s="3"/>
+      <c r="H147" s="3"/>
+      <c r="I147" s="3"/>
+      <c r="J147" s="3"/>
+      <c r="K147" s="3"/>
+      <c r="L147" s="3"/>
+      <c r="M147" s="3"/>
+      <c r="N147" s="3"/>
+      <c r="O147" s="3"/>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A148" s="7">
@@ -6596,16 +6596,28 @@
       <c r="E149" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F149" s="19"/>
-      <c r="G149" s="19"/>
-      <c r="H149" s="19"/>
-      <c r="I149" s="19"/>
-      <c r="J149" s="19"/>
-      <c r="K149" s="19"/>
-      <c r="L149" s="19"/>
-      <c r="M149" s="19"/>
-      <c r="N149" s="19"/>
-      <c r="O149" s="19"/>
+      <c r="F149" s="3">
+        <v>3</v>
+      </c>
+      <c r="G149" s="3">
+        <v>11</v>
+      </c>
+      <c r="H149" s="3">
+        <v>5</v>
+      </c>
+      <c r="I149" s="3">
+        <v>11</v>
+      </c>
+      <c r="J149" s="3">
+        <v>7</v>
+      </c>
+      <c r="K149" s="3">
+        <v>11</v>
+      </c>
+      <c r="L149" s="3"/>
+      <c r="M149" s="3"/>
+      <c r="N149" s="3"/>
+      <c r="O149" s="3"/>
     </row>
     <row r="150" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A150" s="9">
@@ -6623,16 +6635,28 @@
       <c r="E150" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="F150" s="20"/>
-      <c r="G150" s="20"/>
-      <c r="H150" s="20"/>
-      <c r="I150" s="20"/>
-      <c r="J150" s="20"/>
-      <c r="K150" s="20"/>
-      <c r="L150" s="20"/>
-      <c r="M150" s="20"/>
-      <c r="N150" s="20"/>
-      <c r="O150" s="20"/>
+      <c r="F150" s="2">
+        <v>5</v>
+      </c>
+      <c r="G150" s="2">
+        <v>11</v>
+      </c>
+      <c r="H150" s="2">
+        <v>7</v>
+      </c>
+      <c r="I150" s="2">
+        <v>11</v>
+      </c>
+      <c r="J150" s="2">
+        <v>4</v>
+      </c>
+      <c r="K150" s="2">
+        <v>11</v>
+      </c>
+      <c r="L150" s="2"/>
+      <c r="M150" s="2"/>
+      <c r="N150" s="2"/>
+      <c r="O150" s="2"/>
     </row>
     <row r="151" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A151" s="5">
@@ -6650,10 +6674,18 @@
       <c r="E151" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="F151" s="1"/>
-      <c r="G151" s="1"/>
-      <c r="H151" s="1"/>
-      <c r="I151" s="1"/>
+      <c r="F151" s="1">
+        <v>11</v>
+      </c>
+      <c r="G151" s="1">
+        <v>5</v>
+      </c>
+      <c r="H151" s="1">
+        <v>14</v>
+      </c>
+      <c r="I151" s="1">
+        <v>12</v>
+      </c>
       <c r="J151" s="1"/>
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
@@ -6677,12 +6709,24 @@
       <c r="E152" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="F152" s="4"/>
-      <c r="G152" s="4"/>
-      <c r="H152" s="4"/>
-      <c r="I152" s="4"/>
-      <c r="J152" s="4"/>
-      <c r="K152" s="4"/>
+      <c r="F152" s="4">
+        <v>8</v>
+      </c>
+      <c r="G152" s="4">
+        <v>11</v>
+      </c>
+      <c r="H152" s="4">
+        <v>6</v>
+      </c>
+      <c r="I152" s="4">
+        <v>11</v>
+      </c>
+      <c r="J152" s="4">
+        <v>6</v>
+      </c>
+      <c r="K152" s="4">
+        <v>11</v>
+      </c>
       <c r="L152" s="4"/>
       <c r="M152" s="4"/>
       <c r="N152" s="4"/>
@@ -6704,12 +6748,24 @@
       <c r="E153" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="F153" s="3"/>
-      <c r="G153" s="3"/>
-      <c r="H153" s="3"/>
-      <c r="I153" s="3"/>
-      <c r="J153" s="3"/>
-      <c r="K153" s="3"/>
+      <c r="F153" s="3">
+        <v>7</v>
+      </c>
+      <c r="G153" s="3">
+        <v>11</v>
+      </c>
+      <c r="H153" s="3">
+        <v>9</v>
+      </c>
+      <c r="I153" s="3">
+        <v>11</v>
+      </c>
+      <c r="J153" s="3">
+        <v>5</v>
+      </c>
+      <c r="K153" s="3">
+        <v>11</v>
+      </c>
       <c r="L153" s="3"/>
       <c r="M153" s="3"/>
       <c r="N153" s="3"/>
@@ -6731,10 +6787,18 @@
       <c r="E154" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F154" s="2"/>
-      <c r="G154" s="2"/>
-      <c r="H154" s="2"/>
-      <c r="I154" s="2"/>
+      <c r="F154" s="2">
+        <v>10</v>
+      </c>
+      <c r="G154" s="2">
+        <v>12</v>
+      </c>
+      <c r="H154" s="2">
+        <v>2</v>
+      </c>
+      <c r="I154" s="2">
+        <v>11</v>
+      </c>
       <c r="J154" s="2"/>
       <c r="K154" s="2"/>
       <c r="L154" s="2"/>
@@ -6758,12 +6822,24 @@
       <c r="E155" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="F155" s="1"/>
-      <c r="G155" s="1"/>
-      <c r="H155" s="1"/>
-      <c r="I155" s="1"/>
-      <c r="J155" s="1"/>
-      <c r="K155" s="1"/>
+      <c r="F155" s="1">
+        <v>10</v>
+      </c>
+      <c r="G155" s="1">
+        <v>12</v>
+      </c>
+      <c r="H155" s="1">
+        <v>8</v>
+      </c>
+      <c r="I155" s="1">
+        <v>11</v>
+      </c>
+      <c r="J155" s="1">
+        <v>6</v>
+      </c>
+      <c r="K155" s="1">
+        <v>11</v>
+      </c>
       <c r="L155" s="1"/>
       <c r="M155" s="1"/>
       <c r="N155" s="1"/>
@@ -6812,10 +6888,18 @@
       <c r="E157" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F157" s="3"/>
-      <c r="G157" s="3"/>
-      <c r="H157" s="3"/>
-      <c r="I157" s="3"/>
+      <c r="F157" s="3">
+        <v>9</v>
+      </c>
+      <c r="G157" s="3">
+        <v>11</v>
+      </c>
+      <c r="H157" s="3">
+        <v>6</v>
+      </c>
+      <c r="I157" s="3">
+        <v>11</v>
+      </c>
       <c r="J157" s="3"/>
       <c r="K157" s="3"/>
       <c r="L157" s="3"/>

--- a/RESULTADOS T6.xlsx
+++ b/RESULTADOS T6.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{25BA6396-6E0F-4E9F-AD2A-A35379351AF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805D02CB-11A6-4F4E-858E-931AAB4F5755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
@@ -6526,10 +6526,18 @@
       <c r="E147" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F147" s="3"/>
-      <c r="G147" s="3"/>
-      <c r="H147" s="3"/>
-      <c r="I147" s="3"/>
+      <c r="F147" s="3">
+        <v>11</v>
+      </c>
+      <c r="G147" s="3">
+        <v>5</v>
+      </c>
+      <c r="H147" s="3">
+        <v>11</v>
+      </c>
+      <c r="I147" s="3">
+        <v>6</v>
+      </c>
       <c r="J147" s="3"/>
       <c r="K147" s="3"/>
       <c r="L147" s="3"/>
@@ -6861,16 +6869,36 @@
       <c r="E156" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F156" s="3"/>
-      <c r="G156" s="3"/>
-      <c r="H156" s="3"/>
-      <c r="I156" s="3"/>
-      <c r="J156" s="3"/>
-      <c r="K156" s="3"/>
-      <c r="L156" s="3"/>
-      <c r="M156" s="3"/>
-      <c r="N156" s="3"/>
-      <c r="O156" s="3"/>
+      <c r="F156" s="3">
+        <v>9</v>
+      </c>
+      <c r="G156" s="3">
+        <v>11</v>
+      </c>
+      <c r="H156" s="3">
+        <v>16</v>
+      </c>
+      <c r="I156" s="3">
+        <v>14</v>
+      </c>
+      <c r="J156" s="3">
+        <v>11</v>
+      </c>
+      <c r="K156" s="3">
+        <v>6</v>
+      </c>
+      <c r="L156" s="3">
+        <v>10</v>
+      </c>
+      <c r="M156" s="3">
+        <v>12</v>
+      </c>
+      <c r="N156" s="3">
+        <v>11</v>
+      </c>
+      <c r="O156" s="3">
+        <v>8</v>
+      </c>
     </row>
     <row r="157" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A157" s="7">

--- a/RESULTADOS T6.xlsx
+++ b/RESULTADOS T6.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\bots\pp_consulta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{805D02CB-11A6-4F4E-858E-931AAB4F5755}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2B2609E-DA3E-4EC6-8A0C-2641263BEE0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{38F0E9F6-B780-4D16-AEF9-B7D74C50147E}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -126,9 +126,6 @@
     <t>Cristina Gragera</t>
   </si>
   <si>
-    <t>Álvaro Monleon</t>
-  </si>
-  <si>
     <t>Jorge García</t>
   </si>
   <si>
@@ -151,6 +148,9 @@
   </si>
   <si>
     <t>Paula Torres</t>
+  </si>
+  <si>
+    <t>Álvaro Monleón</t>
   </si>
 </sst>
 </file>
@@ -1069,7 +1069,7 @@
         <v>5</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F10" s="4">
         <v>9</v>
@@ -1105,7 +1105,7 @@
         <v>14</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>18</v>
@@ -1140,10 +1140,10 @@
         <v>15</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F12" s="2">
         <v>11</v>
@@ -1308,10 +1308,10 @@
         <v>19</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="F16" s="3">
         <v>4</v>
@@ -1343,10 +1343,10 @@
         <v>20</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F17" s="2">
         <v>11</v>
@@ -1456,7 +1456,7 @@
         <v>24</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>28</v>
@@ -1619,7 +1619,7 @@
         <v>30</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F24" s="4">
         <v>11</v>
@@ -1826,7 +1826,7 @@
         <v>31</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F29" s="1">
         <v>2</v>
@@ -1943,7 +1943,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F32" s="3">
         <v>3</v>
@@ -1979,7 +1979,7 @@
         <v>40</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E33" s="2" t="s">
         <v>21</v>
@@ -2014,7 +2014,7 @@
         <v>41</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>32</v>
@@ -2092,7 +2092,7 @@
         <v>45</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E36" s="2" t="s">
         <v>18</v>
@@ -2127,7 +2127,7 @@
         <v>46</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E37" s="1" t="s">
         <v>29</v>
@@ -2252,7 +2252,7 @@
         <v>50</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>27</v>
@@ -2381,7 +2381,7 @@
         <v>53</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>2</v>
@@ -2584,10 +2584,10 @@
         <v>58</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F48" s="4">
         <v>11</v>
@@ -2623,7 +2623,7 @@
         <v>59</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E49" s="3" t="s">
         <v>29</v>
@@ -2748,7 +2748,7 @@
         <v>63</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>21</v>
@@ -2869,10 +2869,10 @@
         <v>69</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F55" s="3">
         <v>4</v>
@@ -2998,7 +2998,7 @@
         <v>72</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E58" s="3" t="s">
         <v>17</v>
@@ -3037,7 +3037,7 @@
         <v>73</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>31</v>
@@ -3353,7 +3353,7 @@
         <v>84</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E67" s="3" t="s">
         <v>30</v>
@@ -3505,10 +3505,10 @@
         <v>89</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F71" s="3">
         <v>8</v>
@@ -3626,7 +3626,7 @@
         <v>93</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>25</v>
@@ -3668,7 +3668,7 @@
         <v>18</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F75" s="3">
         <v>6</v>
@@ -3700,7 +3700,7 @@
         <v>95</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>31</v>
@@ -3809,10 +3809,10 @@
         <v>100</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F79" s="2">
         <v>11</v>
@@ -3969,7 +3969,7 @@
         <v>104</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E83" s="3" t="s">
         <v>28</v>
@@ -4090,7 +4090,7 @@
         <v>108</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>30</v>
@@ -4206,7 +4206,7 @@
         <v>32</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F89" s="3">
         <v>11</v>
@@ -4324,7 +4324,7 @@
         <v>116</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>29</v>
@@ -4483,7 +4483,7 @@
         <v>21</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F96" s="2">
         <v>7</v>
@@ -4558,7 +4558,7 @@
         <v>125</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E98" s="2" t="s">
         <v>27</v>
@@ -4593,10 +4593,10 @@
         <v>126</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F99" s="1">
         <v>11</v>
@@ -4886,10 +4886,10 @@
         <v>134</v>
       </c>
       <c r="D106" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F106" s="3">
         <v>11</v>
@@ -4967,7 +4967,7 @@
         <v>13</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F108" s="3">
         <v>9</v>
@@ -5046,10 +5046,10 @@
         <v>139</v>
       </c>
       <c r="D110" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F110" s="3">
         <v>11</v>
@@ -5210,10 +5210,10 @@
         <v>143</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F114" s="4">
         <v>4</v>
@@ -5444,7 +5444,7 @@
         <v>152</v>
       </c>
       <c r="D120" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E120" s="3" t="s">
         <v>32</v>
@@ -5646,7 +5646,7 @@
         <v>23</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F125" s="4">
         <v>6</v>
@@ -5811,7 +5811,7 @@
         <v>163</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E129" s="4" t="s">
         <v>28</v>
@@ -5846,7 +5846,7 @@
         <v>164</v>
       </c>
       <c r="D130" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E130" s="3" t="s">
         <v>32</v>
@@ -6014,7 +6014,7 @@
         <v>168</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>18</v>
@@ -6052,7 +6052,7 @@
         <v>31</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F135" s="3">
         <v>5</v>
@@ -6165,7 +6165,7 @@
         <v>30</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F138" s="4">
         <v>7</v>
@@ -6197,7 +6197,7 @@
         <v>174</v>
       </c>
       <c r="D139" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E139" s="3" t="s">
         <v>29</v>
@@ -6279,7 +6279,7 @@
         <v>178</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>27</v>
@@ -6400,7 +6400,7 @@
         <v>183</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E144" s="4" t="s">
         <v>28</v>
@@ -6485,7 +6485,7 @@
         <v>26</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="F146" s="1">
         <v>11</v>
@@ -6521,7 +6521,7 @@
         <v>187</v>
       </c>
       <c r="D147" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E147" s="3" t="s">
         <v>21</v>
@@ -6790,10 +6790,10 @@
         <v>195</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="F154" s="2">
         <v>10</v>
@@ -6911,7 +6911,7 @@
         <v>199</v>
       </c>
       <c r="D157" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E157" s="3" t="s">
         <v>27</v>
